--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samjo/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26AF0704-DD87-2544-96E4-31CCDA2F6390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7705B6-6A46-CF48-A2FA-8C775014E3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35740" yWindow="6760" windowWidth="31040" windowHeight="22040" activeTab="6" xr2:uid="{6AA5D1E0-5045-0A44-A426-F5E527A1D1E1}"/>
+    <workbookView xWindow="37960" yWindow="7460" windowWidth="30720" windowHeight="21680" firstSheet="2" activeTab="7" xr2:uid="{6AA5D1E0-5045-0A44-A426-F5E527A1D1E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Financial Statements" sheetId="6" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="Peer Analysis" sheetId="8" r:id="rId3"/>
     <sheet name="Valuation Model" sheetId="9" r:id="rId4"/>
     <sheet name="Analysis &amp; Summary" sheetId="11" r:id="rId5"/>
-    <sheet name="Company Overview" sheetId="10" r:id="rId6"/>
-    <sheet name="Claude Log" sheetId="5" r:id="rId7"/>
+    <sheet name="Management &amp; Governance" sheetId="12" r:id="rId6"/>
+    <sheet name="Company Overview" sheetId="10" r:id="rId7"/>
+    <sheet name="Claude Log" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -1172,6 +1173,1753 @@
     <author>Samuel Jo</author>
   </authors>
   <commentList>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{C69EF2F3-E6CC-084E-A506-6DAA7AB8D53D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{8B6F75C3-94D7-EC4E-9BB3-65F75789BB95}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team &amp; Crunchbase</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00200B5E-A299-2C45-9B55-8C979AE674EE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{5667B82A-64FB-C34D-AF8A-D91DFE110065}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com, Feb 27 2025 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{EE9A3175-D15A-CE49-B00E-2878087A7650}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: battery-tech.net company profile</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{BEB49E3F-B798-A644-90CA-E9DE44C4A6EB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{4130B63B-368C-AB43-A066-8195A3A7AC9B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{983CAD7B-BC44-7F46-98A2-E875FEA2F3B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com, Feb 27 2025 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{DE95A305-2B19-DE4B-846E-E12F5180D85D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: battery-tech.net company profile</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{13E1A8BE-E6DD-8447-81B7-588A08AC2CB5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team &amp; Crunchbase</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{4958DEA0-245D-444A-82B8-EC83BF3DEF6F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.16-17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{5CB5D762-E7B8-0D48-BE3B-7A90980C827E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 Interim FS, Note 13</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{584DFEE9-0586-774E-84B3-FA0F310EFBB8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: battery-tech.net company profile</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{7609CD30-E57A-3740-B769-9B61766092B3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{CF40531D-5963-554D-91D8-F93E5C3F1FCC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com, Feb 27 2025 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{D05B3495-4561-A647-B84D-9EA00BC3946B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{C5B325EF-DE1E-4544-BE12-EF0A19359D1D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{6F77E891-2279-DA40-9F22-FDD9D932A424}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com, Feb 27 2025 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{29AC5882-0475-D642-AD98-995D043481B9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{A4843A8B-C3C1-F846-A081-3F570AD0CFA5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{C7203EAC-0023-FC47-B34E-9434E0A56BFB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{384CB76B-B03E-E343-8F62-FC01A1D9954F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{11650526-4317-164E-A421-8C17C2AF605F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{17EB7824-FD53-D349-8866-10484695FA1A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{0774D674-451F-2148-8898-5703CC4CFA78}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{61EB27A8-CB2D-4744-8E3E-6C62AA024DFD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com, Feb 27 2025 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{C1E181F0-9ADB-5944-A3C4-92E97FD50AE5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: battery-tech.net company profile</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{9B2D4B9C-1A04-024E-92B9-CB4F3B8C4FA7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0" shapeId="0" xr:uid="{F492B796-7405-CD4D-A70E-6E0B27527EE8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D17" authorId="0" shapeId="0" xr:uid="{B106B3AB-E742-034B-82D9-7ACCAC567805}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Yahoo Finance, Oct 19 2022 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0" xr:uid="{D2808DD7-09B8-434A-A1E5-4ACA00DC1E98}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Yahoo Finance, Oct 19 2022 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{BB34DAD4-A659-014D-8F25-3BE745992A58}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{37B55038-E204-8C4F-BE1A-77E606EA5F81}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{B4DFF4FD-6784-E741-8F7F-C5A04F293479}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{58D3F025-8226-C746-B593-EA025931E8C0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{02426408-19AA-D940-889E-02E3B08F2273}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/GaryStanley</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0" shapeId="0" xr:uid="{FAD13200-B491-A44A-8A5F-EBC3521F34B2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/GaryStanley</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D19" authorId="0" shapeId="0" xr:uid="{F8C1E0DA-0ABE-8D45-BE61-7284586BCB80}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com, Nov 7 2025 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{49210EE2-4EB9-8840-B195-2C1875E9C337}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Proactive Investors, Apr 17 2024</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{657EB2E6-43A5-0248-8D48-B96036A6EB24}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0" xr:uid="{D9D2A377-8E5B-FF41-A191-DD78CC294510}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{316606FF-391C-FA43-B9F6-F254C4220360}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0" xr:uid="{073447E8-3DF7-394F-844E-686CC6C2E981}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{DD9C25EC-AC36-B342-BB6D-6C88F5C514C3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{DDAF521B-BAE8-6947-ACF7-293039F759F4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0" xr:uid="{73E8805E-8C25-5348-9BA7-017F073D9116}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="0" shapeId="0" xr:uid="{D4B36C50-8B63-4F41-B5FE-B1C77D592EFB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{EE871EE7-4B48-2F41-863A-2B3DB669202B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{7EE73119-20A0-C64F-A38D-E2C54D6AC41F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0" xr:uid="{8C28AD6D-D421-0346-B8F9-ECE96A586E04}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0" xr:uid="{9FEB6BEB-E77C-9647-8FD0-AB0637537376}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{600CAFBD-4178-3D4F-9F26-B5BE5C71BF35}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0" shapeId="0" xr:uid="{043DE727-5705-F947-9BA9-504F19A8E92D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0" xr:uid="{650453DC-D7B2-3645-BA82-15B646636C81}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{D1F2644A-A021-4A41-874F-4EF47619CCAD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0" xr:uid="{D05F91A2-EF79-EF44-A19D-CF3AD560159B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="0" shapeId="0" xr:uid="{A3C6D0CC-2980-5741-88EA-E0F623D105C4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0" xr:uid="{423374A6-CA7E-B245-8535-C43F1BDB1F7B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{A32E1904-8E6E-0B4B-B71A-52238065E72B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{4A27D3CD-7A0A-A04B-8ABF-ADACDE0AE8D2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="0" shapeId="0" xr:uid="{DC412DB2-55A5-8B49-90F8-4E0A41E8497B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0" xr:uid="{28FDBE13-CC8E-5244-A2A5-0D9B989E1945}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{9FB52145-2B54-5C4B-A14E-A32E0A84E1EA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0" xr:uid="{07FACDE2-7C7B-0848-9F0E-0A9C8667A9D2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C32" authorId="0" shapeId="0" xr:uid="{3A442995-AB94-AE45-99F3-575DCE5F1D21}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com/team</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0" xr:uid="{D8F2CEBE-6775-D940-BDE8-1CA1A3467623}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0" xr:uid="{47CCDFE6-AEF3-1544-9121-C3F8382ADBD4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.10</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0" shapeId="0" xr:uid="{7AE61652-B8A5-584E-86C1-C38D6E46619A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com, Feb 27 2025 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0" xr:uid="{798512FF-4FC1-6A47-9640-15E1DA5B46A4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.13</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0" xr:uid="{6A55BB1F-CD5D-F640-9D5E-0178814FCB1F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0" xr:uid="{A076238E-53FA-684B-BA79-F949E2CD45F2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: firstphosphate.com, Feb 27 2025 NR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0" xr:uid="{32EF2BC7-3B30-384B-8858-B8F9E9B37580}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Samuel Jo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: Q3 MDA FY2026, p.17</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Samuel Jo</author>
+  </authors>
+  <commentList>
     <comment ref="E5" authorId="0" shapeId="0" xr:uid="{99530043-DFFD-7447-A3A0-CD1D8C3280A5}">
       <text>
         <r>
@@ -1321,7 +3069,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="952">
   <si>
     <t>COMPANY SNAPSHOT</t>
   </si>
@@ -1416,6 +3164,12 @@
     <t>Royalties</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>~6.1%</t>
+  </si>
+  <si>
     <t>Junior Avg</t>
   </si>
   <si>
@@ -1495,6 +3249,15 @@
   </si>
   <si>
     <t>Advanced Stage</t>
+  </si>
+  <si>
+    <t>OVERALL ASSESSMENT</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Detail</t>
   </si>
   <si>
     <t>Total Assets</t>
@@ -3567,6 +5330,633 @@
   </si>
   <si>
     <t>Verified ✅. Claude Log moved to last tab. All data intact.</t>
+  </si>
+  <si>
+    <t>FIRST PHOSPHATE CORP. — MANAGEMENT &amp; GOVERNANCE ANALYSIS</t>
+  </si>
+  <si>
+    <t>Board of Directors, Executive Officers, Advisory Board, Key Staff &amp; Insider Activity</t>
+  </si>
+  <si>
+    <t>Sources: SEDAR+ Filings (Annual FS, Quarterly Interims, MDA Q1-Q3 FY2026) &amp; firstphosphate.com/team</t>
+  </si>
+  <si>
+    <t>SECTION 1: EXECUTIVE OFFICERS &amp; BOARD OF DIRECTORS</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Title / Role</t>
+  </si>
+  <si>
+    <t>Background &amp; Expertise</t>
+  </si>
+  <si>
+    <t>Key Relationships / Entities</t>
+  </si>
+  <si>
+    <t>Compensation (9mo Nov 30, 2025)</t>
+  </si>
+  <si>
+    <t>Insider Buying</t>
+  </si>
+  <si>
+    <t>Est. Ownership %</t>
+  </si>
+  <si>
+    <t>John Passalacqua</t>
+  </si>
+  <si>
+    <t>CEO &amp; Director</t>
+  </si>
+  <si>
+    <t>Int'l MBA (Schulich/York). 35+ yrs technology &amp; capital markets. Top 50 int'l business strategist (1998). Fluently bilingual (French/English). Previously President of ExpoWorld Ltd.</t>
+  </si>
+  <si>
+    <t>ExpoWorld Ltd. (personal holding co). Audit Committee member.</t>
+  </si>
+  <si>
+    <t>$341,704 (100% RSUs/options; $0 cash salary)</t>
+  </si>
+  <si>
+    <t>2,872,000 shares purchased (~C$1.8M) since May 2023. 811,000 in 2025 alone ($262K).</t>
+  </si>
+  <si>
+    <t>~17.3%</t>
+  </si>
+  <si>
+    <t>STRONG. Largest individual shareholder. Takes 100% comp in equity — maximum alignment. Active media presence (PDAC, Toronto Global Forum, investor conferences). Hands-on CEO driving LFP narrative.</t>
+  </si>
+  <si>
+    <t>Laurence W. Zeifman, CPA</t>
+  </si>
+  <si>
+    <t>Chairman &amp; Independent Director</t>
+  </si>
+  <si>
+    <t>Audit partner, Zeifmans LLP (mid-sized Toronto CPA firm). 4 decades public accounting. Former Chair, Nexia Canada (int'l accounting network). Former Director, Ottawa Senators / Alternate Governor, NHL.</t>
+  </si>
+  <si>
+    <t>Z Six Financial Corp. (with spouse). Chair of Audit Committee. Member of Compensation Committee.</t>
+  </si>
+  <si>
+    <t>$127,430 (100% RSUs/options; $0 cash)</t>
+  </si>
+  <si>
+    <t>359,500 shares purchased ($74,390) since IPO Feb 2023. 40,000 in 2025 ($7,475).</t>
+  </si>
+  <si>
+    <t>STRONG. Top-tier CPA credentials. Decades of audit experience critical for pre-revenue company needing clean financials. Open market buying signals conviction. Board independence well-established.</t>
+  </si>
+  <si>
+    <t>Bennett Kurtz</t>
+  </si>
+  <si>
+    <t>CAO, CFO, Corporate Secretary &amp; Director</t>
+  </si>
+  <si>
+    <t>Principal of Kurtz Financial Group. York University (Liberal Arts). Experience taking private companies public. Multi-faceted: finance, management, sales, marketing, analytics.</t>
+  </si>
+  <si>
+    <t>POF Capital Corp. (personal holding co). Also serves as IR contact.</t>
+  </si>
+  <si>
+    <t>$168,834 (100% RSUs/options; $0 cash)</t>
+  </si>
+  <si>
+    <t>Ongoing participation in placements.</t>
+  </si>
+  <si>
+    <t>~5.4%</t>
+  </si>
+  <si>
+    <t>ADEQUATE. Wears many hats (CAO/CFO/Secretary/Director/IR). Capital markets experience relevant for a company needing constant financing. Risk: multi-role may strain capacity as company scales.</t>
+  </si>
+  <si>
+    <t>Armand MacKenzie</t>
+  </si>
+  <si>
+    <t>President (promoted May 2025)</t>
+  </si>
+  <si>
+    <t>Raised in traditional Innu territory. 15 yrs practicing law — chief legal advisor on land rights for Innu Nation. UN special advisor/negotiator on Declaration of Rights of Indigenous Peoples. 15 yrs as mining executive. Negotiated numerous impact benefit agreements.</t>
+  </si>
+  <si>
+    <t>Leading Indigenous partnership discussions with Pekuakamiulnuatsh First Nation. Ensuring deep Indigenous financial participation.</t>
+  </si>
+  <si>
+    <t>$88,166 (100% RSUs/options; $0 cash)</t>
+  </si>
+  <si>
+    <t>CRITICAL ASSET. Uniquely qualified for Indigenous relations — literally helped draft UN Indigenous Rights Declaration. Mining executive background. Promotion to President signals strategic priority of Indigenous partnerships for permitting &amp; social license.</t>
+  </si>
+  <si>
+    <t>David Dufour</t>
+  </si>
+  <si>
+    <t>Senior Vice-President (promoted May 2025)</t>
+  </si>
+  <si>
+    <t>30+ years experience in development and management of high-growth businesses in Saguenay, Quebec. Deep local knowledge of the region.</t>
+  </si>
+  <si>
+    <t>Drives operations and community relations for feasibility study planning.</t>
+  </si>
+  <si>
+    <t>$101,062 (100% RSUs/options; $0 cash)</t>
+  </si>
+  <si>
+    <t>GOOD. Local Saguenay roots essential for community buy-in. Operations focus needed as company transitions from exploration to development. Promotion signals increased operational readiness.</t>
+  </si>
+  <si>
+    <t>Gilles Laverdière, P.Geo</t>
+  </si>
+  <si>
+    <t>Chief Geologist</t>
+  </si>
+  <si>
+    <t>40+ years mining exploration in Quebec. Former President &amp; CEO of HMZ Metals Inc. Senior executive and board member of many public mining cos. Member, Ordre des Géologues du Québec. Qualified Person under NI 43-101.</t>
+  </si>
+  <si>
+    <t>166693 Canada Inc. (personal co). Receives part compensation as cash for mining exploration work ($194,880 in 9mo).</t>
+  </si>
+  <si>
+    <t>$217,543 ($194,880 cash + $22,663 options)</t>
+  </si>
+  <si>
+    <t>STRONG. Only officer receiving meaningful cash comp — justified as hands-on geological work. QP status essential for NI 43-101 compliance. 40+ yrs Quebec mining experience is exactly what's needed.</t>
+  </si>
+  <si>
+    <t>Peter Nicholson</t>
+  </si>
+  <si>
+    <t>Independent Director (joined Sep 2024)</t>
+  </si>
+  <si>
+    <t>Recognized leader in Canadian tax-assisted investments. Focus on philanthropic tax planning and mining industry. Helped generate $350M+ for client donations. Philanthropist.</t>
+  </si>
+  <si>
+    <t>WPCD Inc. Chair of Compensation Committee. Member of Audit Committee.</t>
+  </si>
+  <si>
+    <t>$100,486 (100% RSUs/options; $0 cash)</t>
+  </si>
+  <si>
+    <t>532,000 shares purchased ($146,415) since joining Sep 2024. 197,500 in 2025 ($58,945).</t>
+  </si>
+  <si>
+    <t>~2.8%</t>
+  </si>
+  <si>
+    <t>STRONG. Tax-assisted investment expertise directly relevant to flow-through share financings (PHOS's primary funding method). Aggressive open market buying despite being newest director signals deep conviction.</t>
+  </si>
+  <si>
+    <t>SECTION 2: ADVISORY BOARD</t>
+  </si>
+  <si>
+    <t>Advisory Role / Specialty</t>
+  </si>
+  <si>
+    <t>Relevance to PHOS</t>
+  </si>
+  <si>
+    <t>Joined</t>
+  </si>
+  <si>
+    <t>Key Accomplishments</t>
+  </si>
+  <si>
+    <t>Strategic Value</t>
+  </si>
+  <si>
+    <t>Yves Caprara</t>
+  </si>
+  <si>
+    <t>Phosphoric Acid Technology Expert</t>
+  </si>
+  <si>
+    <t>Former CEO, Prayon SA (Europe's largest producer of food &amp; technical grade phosphoric acid). Operations across Europe, US, Canada, China, India, Brazil, Morocco. Board member, Int'l Fertilizer Association (2015-2020).</t>
+  </si>
+  <si>
+    <t>DIRECTLY relevant to PHOS's core business of purified phosphoric acid (PPA) production. Co-authored "Identifying the Pinch Points in the LFP Supply Chain" (Battery Metals Review, Feb 2022).</t>
+  </si>
+  <si>
+    <t>Ran Prayon SA globally. Foresaw LFP supply shocks by 2025-2030. Industry thought leader on phosphate-to-LFP value chain.</t>
+  </si>
+  <si>
+    <t>★★★★★</t>
+  </si>
+  <si>
+    <t>EXCEPTIONAL. The single most relevant advisor for PHOS's core thesis. His Prayon experience is a direct parallel to what PHOS is building. Global phosphoric acid market knowledge is irreplaceable.</t>
+  </si>
+  <si>
+    <t>Bernard Lapointe, PhD</t>
+  </si>
+  <si>
+    <t>Quebec Phosphate Development Expert</t>
+  </si>
+  <si>
+    <t>Founded Arianne Phosphate in 1997, President until 2013. PhD in mineral resources (UQAC). Former Director, Saguenay-Lac-St-Jean Mining Fund. Board member of several public resource cos.</t>
+  </si>
+  <si>
+    <t>Founded the ONLY other significant phosphate company in Quebec (Arianne / DAN). Intimate knowledge of Saguenay region geology and permitting.</t>
+  </si>
+  <si>
+    <t>Pre-2023</t>
+  </si>
+  <si>
+    <t>Built Arianne Phosphate from concept to advanced-stage phosphate project. Deep Quebec mining fund relationships.</t>
+  </si>
+  <si>
+    <t>EXCEPTIONAL. Literally the person who proved phosphate viability in Saguenay-Lac-St-Jean. His involvement validates PHOS's geological thesis. Relationships with Quebec mining funds invaluable.</t>
+  </si>
+  <si>
+    <t>Gary Stanley</t>
+  </si>
+  <si>
+    <t>US Critical Minerals Policy Expert</t>
+  </si>
+  <si>
+    <t>Former Director, Office of Critical Minerals &amp; Metals at U.S. Department of Commerce. 40+ years serving under every US President from Reagan to Biden. Lead author, 2019 US Federal Critical Minerals Strategy.</t>
+  </si>
+  <si>
+    <t>Phosphate added to US Critical Minerals List in Nov 2025. Stanley's strategy work was foundational for this. Direct access to US policy ecosystem.</t>
+  </si>
+  <si>
+    <t>Created 2019 USA-Canada Critical Minerals Working Group. Led policy that became foundation for US critical mineral supply chain prerogatives.</t>
+  </si>
+  <si>
+    <t>EXCEPTIONAL. Phosphate's addition to US Critical Minerals List makes his connections priceless. Access to US DOE/DOC funding streams, fast-track permitting advocacy, and Canada-US cooperation frameworks.</t>
+  </si>
+  <si>
+    <t>Paul Pitman, P.Geo</t>
+  </si>
+  <si>
+    <t>Geological Advisor</t>
+  </si>
+  <si>
+    <t>50+ years as exploration geologist, corporate officer, and geological consultant. Founded/directed several junior resource cos including 3 fertilizer companies: Pueblo Potash, Murdock Mt. (phosphate), Boreal Agrominerals.</t>
+  </si>
+  <si>
+    <t>Phosphate-specific geological expertise. Multiple fertilizer company experience bridges geology-to-market gap.</t>
+  </si>
+  <si>
+    <t>Founded 3 fertilizer companies. Half-century of mining exploration and corporate officer experience.</t>
+  </si>
+  <si>
+    <t>★★★★☆</t>
+  </si>
+  <si>
+    <t>STRONG. Phosphate-specific geology experience across multiple companies. Rare to find geological consultants with fertilizer-specific track record.</t>
+  </si>
+  <si>
+    <t>Ford Nicholson</t>
+  </si>
+  <si>
+    <t>Energy &amp; Finance Advisor</t>
+  </si>
+  <si>
+    <t>Managing Partner &amp; founder, Kepis &amp; Pobe Financial Group. 25+ years investing in and managing international energy projects (traditional &amp; renewable). Former Deputy Chairman, InterOil Corp (sold to ExxonMobil). Former member, President's Council, Int'l Crisis Group.</t>
+  </si>
+  <si>
+    <t>Major project financing experience. InterOil sale to ExxonMobil demonstrates ability to shepherd major resource transactions.</t>
+  </si>
+  <si>
+    <t>InterOil → ExxonMobil sale was multi-billion dollar transaction. Deep international project finance network.</t>
+  </si>
+  <si>
+    <t>STRONG. Experience bringing resource companies from development to major transaction/sale. Valuable for PHOS's eventual capex financing and potential strategic partnerships.</t>
+  </si>
+  <si>
+    <t>Dr. Peir Pufahl, P.Geo</t>
+  </si>
+  <si>
+    <t>Scientific/Geological Advisor</t>
+  </si>
+  <si>
+    <t>Professor of Earth Science, Queen's University. Co-director, Queen's Facility for Isotope Research. Internationally recognized expert on phosphorite geology. Fellow of Society of Economic Geologists and Geological Society of America.</t>
+  </si>
+  <si>
+    <t>Developed state-of-the-art phosphorite exploration models. Directly partnered with PHOS on Lac à l'Orignal mineralogy and geochemistry work.</t>
+  </si>
+  <si>
+    <t>World-class academic credentials in phosphorite geology. Direct research partnership with PHOS.</t>
+  </si>
+  <si>
+    <t>STRONG. Academic credibility adds scientific validation to PHOS's resource claims. Phosphorite-specific expertise is extremely rare. Queen's partnership adds institutional weight.</t>
+  </si>
+  <si>
+    <t>Mario Bouchard</t>
+  </si>
+  <si>
+    <t>Quebec Government Relations / Project Development Mgr</t>
+  </si>
+  <si>
+    <t>Former Assistant Deputy Minister for Strategic Industries &amp; Major Economic Projects (Quebec Ministry of Economy &amp; Innovation). Also former Associate Deputy Minister for Energy, Natural Resources &amp; Finance. Involved in major corporate financing by Quebec government, creation of state-owned companies, privatizations.</t>
+  </si>
+  <si>
+    <t>Direct experience with Quebec government financing of major projects. Understands provincial funding mechanisms, subsidies, and permitting.</t>
+  </si>
+  <si>
+    <t>Pre-2024</t>
+  </si>
+  <si>
+    <t>Led Quebec's industrial project financing at ministerial level. Created/privatized state-owned companies.</t>
+  </si>
+  <si>
+    <t>EXCEPTIONAL. Quebec government financing will be CRITICAL for PHOS's US$459M capex. His insider knowledge of provincial funding mechanisms, critical minerals subsidies, and political relationships is invaluable.</t>
+  </si>
+  <si>
+    <t>SECTION 3: KEY OPERATIONAL STAFF</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Experience</t>
+  </si>
+  <si>
+    <t>Key Capabilities</t>
+  </si>
+  <si>
+    <t>Arnab De</t>
+  </si>
+  <si>
+    <t>Corporate Finance Director</t>
+  </si>
+  <si>
+    <t>20+ yrs financial management, planning, business optimization &amp; strategy development. Worked for Tata Group as CFO in JCAPCPL joint venture (Nippon Steel &amp; Tata Steel Minerals Canada). Oversaw DSO project from conception.</t>
+  </si>
+  <si>
+    <t>Managed +$1.5B in equity/debt investment at Tata Group. Major project financing expertise directly applicable to PHOS's capex needs.</t>
+  </si>
+  <si>
+    <t>20+ years</t>
+  </si>
+  <si>
+    <t>Large-scale mining project finance. Tata/Nippon Steel JV experience. Equity &amp; debt structuring.</t>
+  </si>
+  <si>
+    <t>STRONG. Tata Group experience with $1.5B+ project is directly relevant to PHOS's US$459M capex. Adds credibility with institutional investors and lenders.</t>
+  </si>
+  <si>
+    <t>Steeve Lavoie, P.Geo</t>
+  </si>
+  <si>
+    <t>Geology Manager</t>
+  </si>
+  <si>
+    <t>BSc Geology (UQAC - environmental concentration). 20+ yrs mineral exploration. Planned/supervised drilling projects in Quebec &amp; Nunavut. Participated in 2 mining project start-ups for Agnico Eagle Mines.</t>
+  </si>
+  <si>
+    <t>Agnico Eagle experience = production-level mining. Community relations for mine start-ups directly relevant.</t>
+  </si>
+  <si>
+    <t>Drilling supervision. Mine start-up experience (Agnico Eagle). Local community engagement.</t>
+  </si>
+  <si>
+    <t>GOOD. Agnico Eagle start-up experience is rare and relevant. UQAC education keeps him rooted in the Saguenay region.</t>
+  </si>
+  <si>
+    <t>Yves Desrosiers, Eng.</t>
+  </si>
+  <si>
+    <t>Director of Mining Operations</t>
+  </si>
+  <si>
+    <t>Metallurgical engineer. Managed major site operations and engineering projects in mining (manager, GM, VP levels). Knowledge: mining, concentrators, engineering, environment, H&amp;S, maintenance.</t>
+  </si>
+  <si>
+    <t>Focus on production costs while respecting deadlines and budgets. Critical for transition from exploration to feasibility.</t>
+  </si>
+  <si>
+    <t>Site operations management. Metallurgical engineering. Cost control and budget management.</t>
+  </si>
+  <si>
+    <t>GOOD. Practical mine operations experience needed as PHOS prepares feasibility study. Metallurgical engineering directly relevant to processing.</t>
+  </si>
+  <si>
+    <t>Mehrdad Taheran</t>
+  </si>
+  <si>
+    <t>Metallurgy / R&amp;D</t>
+  </si>
+  <si>
+    <t>Chemical engineering and water sciences background. 15+ years in research, product development, project management. Specializes in optimizing extraction and refining processes.</t>
+  </si>
+  <si>
+    <t>Directly relevant to PHOS's hydrometallurgical processing of anorthosite rock into purified phosphoric acid.</t>
+  </si>
+  <si>
+    <t>15+ years</t>
+  </si>
+  <si>
+    <t>Extraction &amp; refining optimization. Metallurgical R&amp;D. Product quality assurance.</t>
+  </si>
+  <si>
+    <t>GOOD. Technical backbone for hydromet processing. Essential for achieving battery-grade purity specifications.</t>
+  </si>
+  <si>
+    <t>Valérie Morin</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Experience in accounting firms (audit, assurance, advisory). Worked with organizations across a wide range of business models. Rigorous financial perspective on project viability and economic potential.</t>
+  </si>
+  <si>
+    <t>Supports informed investment decisions. Financial analysis and project economics expertise.</t>
+  </si>
+  <si>
+    <t>Audit &amp; assurance background. Project economic viability assessment.</t>
+  </si>
+  <si>
+    <t>ADEQUATE. Provides additional financial analysis capacity alongside CFO Kurtz.</t>
+  </si>
+  <si>
+    <t>Alexis de la Renaudière</t>
+  </si>
+  <si>
+    <t>Team Lead, Strategic Development</t>
+  </si>
+  <si>
+    <t>Business development professional with extensive capital markets experience.</t>
+  </si>
+  <si>
+    <t>Strategic development and business origination for partnerships, offtakes, and financings.</t>
+  </si>
+  <si>
+    <t>Capital markets. Strategic business development.</t>
+  </si>
+  <si>
+    <t>ADEQUATE. Supports CEO on business development and capital markets outreach.</t>
+  </si>
+  <si>
+    <t>SECTION 4: COMPENSATION STRUCTURE &amp; INSIDER ACTIVITY ANALYSIS</t>
+  </si>
+  <si>
+    <t>Compensation Philosophy</t>
+  </si>
+  <si>
+    <t>Investor Implication</t>
+  </si>
+  <si>
+    <t>CEO takes 100% comp in RSUs/options</t>
+  </si>
+  <si>
+    <t>John Passalacqua receives $0 cash salary. All comp ($341,704 in 9mo) is equity-based.</t>
+  </si>
+  <si>
+    <t>Maximum alignment — CEO only benefits if share price rises. Preserves cash for operations. Extremely rare for junior mining CEOs.</t>
+  </si>
+  <si>
+    <t>Board receives 100% comp in RSUs</t>
+  </si>
+  <si>
+    <t>Since Sep 1, 2023, all director fees are paid via RSU issuance. $0 cash director fees.</t>
+  </si>
+  <si>
+    <t>Board fully aligned with shareholders. No cash drain for governance costs.</t>
+  </si>
+  <si>
+    <t>Management receives ~80% in RSUs</t>
+  </si>
+  <si>
+    <t>Officers receive majority of compensation in equity. Exception: Chief Geologist receives cash for hands-on exploration work ($194,880).</t>
+  </si>
+  <si>
+    <t>Cash-conserving comp structure. Only exception is justified (on-site geological work requires cash).</t>
+  </si>
+  <si>
+    <t>Omnibus Equity Incentive Plan</t>
+  </si>
+  <si>
+    <t>Rolling plan: up to 20% of shares outstanding reserved for options + RSUs. Replaced Legacy Stock Option Plan (Aug 2023). As at Nov 30, 2025: 14,578,400 shares reserved (~9.6% of outstanding).</t>
+  </si>
+  <si>
+    <t>20% rolling cap is standard for juniors but creates dilution risk. 9.6% currently allocated is moderate.</t>
+  </si>
+  <si>
+    <t>★★★☆☆</t>
+  </si>
+  <si>
+    <t>Total key mgmt comp (9mo FY2026)</t>
+  </si>
+  <si>
+    <t>$1,261,232 (vs $1,282,316 in 9mo FY2025). Includes: share-based comp $928,654 + financing fees $332,578.</t>
+  </si>
+  <si>
+    <t>Flat YoY despite significant company growth (shares: 90M → 151M). Disciplined cost control on mgmt comp.</t>
+  </si>
+  <si>
+    <t>CEO insider buying (open market)</t>
+  </si>
+  <si>
+    <t>2,872,000 shares (~C$1.8M) purchased since May 2023 with personal capital. 811,000 shares ($262K) in 2025 alone.</t>
+  </si>
+  <si>
+    <t>Massive signal. CEO buying at same prices available to retail investors. $1.8M is significant relative to company size.</t>
+  </si>
+  <si>
+    <t>Director/insider buying (combined)</t>
+  </si>
+  <si>
+    <t>Chairman Zeifman: 359,500 shares ($74K). Director Nicholson: 532,000 shares ($146K). Officers/directors also participated in private placements: 1,560,224 shares + 108,950 warrants exercised in 9mo FY2026.</t>
+  </si>
+  <si>
+    <t>Broad insider buying across multiple insiders = collective conviction. Nicholson buying aggressively despite being newest member.</t>
+  </si>
+  <si>
+    <t>SECTION 5: OVERALL MANAGEMENT ASSESSMENT</t>
+  </si>
+  <si>
+    <t>Strengths</t>
+  </si>
+  <si>
+    <t>Weaknesses / Risks</t>
+  </si>
+  <si>
+    <t>Executive Leadership</t>
+  </si>
+  <si>
+    <t>CEO 100% equity comp + $1.8M personal buying = exceptional alignment. Strong narrative builder (PDAC, Toronto Global Forum). Deep bilingual capability for Quebec operations. Team promotions (MacKenzie → President, Dufour → SVP) show organizational maturity.</t>
+  </si>
+  <si>
+    <t>CEO multi-tasking risk — heads strategy, IR, govt relations, media. No dedicated COO. CFO/CAO/Secretary/IR = too many hats for one person (Kurtz). No succession plan disclosed.</t>
+  </si>
+  <si>
+    <t>Board Independence</t>
+  </si>
+  <si>
+    <t>2 of 5 directors are independent (Zeifman, Nicholson). Both are active open-market buyers. Audit Committee chaired by experienced CPA. Compensation Committee established.</t>
+  </si>
+  <si>
+    <t>Only 2/5 independent directors — below TSX Venture best practice of majority independent. CEO + CFO + President on board = management-heavy. No Nominating/Governance Committee disclosed.</t>
+  </si>
+  <si>
+    <t>Technical Expertise</t>
+  </si>
+  <si>
+    <t>Chief Geologist (40+ yrs, QP). Advisory board includes world-class phosphate experts: Caprara (Prayon CEO), Lapointe (founded Arianne), Pufahl (Queen's). Metallurgy, mining ops, and geology all covered in-house.</t>
+  </si>
+  <si>
+    <t>No in-house chemical engineering lead for phosphoric acid plant design. Will need to hire or contract significant technical capacity for feasibility/construction phase.</t>
+  </si>
+  <si>
+    <t>Strategic Relationships</t>
+  </si>
+  <si>
+    <t>Stanley (US Critical Minerals policy), Bouchard (Quebec govt financing), MacKenzie (Indigenous relations / UN), Nicholson (major project M&amp;A). Covers all four critical stakeholder groups: government, Indigenous, capital markets, industry.</t>
+  </si>
+  <si>
+    <t>Advisory board members are not employees — they may have competing commitments. No disclosed retainer or exclusivity agreements for advisors.</t>
+  </si>
+  <si>
+    <t>Compensation Alignment</t>
+  </si>
+  <si>
+    <t>Near-zero cash burn on management comp. CEO, Chairman, CFO, President, SVP, newest Director ALL take 100% equity. Flat total comp YoY despite company growth. 20% omnibus cap is standard.</t>
+  </si>
+  <si>
+    <t>Equity-heavy comp creates dilution (14.6M shares reserved = 9.6% of outstanding). If share price declines, retention risk increases. Omnibus plan allows up to 20% dilution.</t>
+  </si>
+  <si>
+    <t>Insider Conviction</t>
+  </si>
+  <si>
+    <t>CEO ($1.8M open market), Chairman ($74K), Director Nicholson ($146K). Broad-based buying across multiple insiders at retail prices. Officers participated in private placements (1.56M shares + 109K warrants in 9mo FY2026).</t>
+  </si>
+  <si>
+    <t>Insiders also receive shares as comp — total insider ownership may overstate conviction if majority is granted vs. purchased. ~17% CEO ownership creates key-man dependency.</t>
+  </si>
+  <si>
+    <t>Operational Readiness</t>
+  </si>
+  <si>
+    <t>Geology Manager (Agnico Eagle start-ups), Mining Ops Director (metallurgical eng.), Corporate Finance Director (Tata $1.5B+ projects), Metallurgy/R&amp;D lead. Covers geology → mining → processing → finance pipeline.</t>
+  </si>
+  <si>
+    <t>Team is still exploration-stage sized (~12-15 people). Feasibility and construction will require 10x+ headcount. No disclosed recruitment pipeline or organizational scaling plan.</t>
+  </si>
+  <si>
+    <t>ABOVE AVERAGE FOR STAGE. Management team is exceptionally well-assembled for a pre-revenue junior miner. Insider buying, equity-only comp, and advisory board depth are rare at this market cap. The team covers all critical competencies: phosphate technology (Caprara), Quebec geology (Lapointe/Laverdière), US policy (Stanley), Indigenous relations (MacKenzie), Quebec govt finance (Bouchard), and major project execution (De/Nicholson).</t>
+  </si>
+  <si>
+    <t>KEY RISKS: (1) Key-man dependency on CEO Passalacqua. (2) CFO role overextended. (3) Board independence below best practice. (4) Team scaling for feasibility/construction not yet addressed. (5) Advisory board retention uncertain. These are TYPICAL for junior miners at this stage and do not outweigh the strengths.</t>
+  </si>
+  <si>
+    <t>User asked if Management &amp; Governance sheet was complete and if any further improvements were needed.</t>
+  </si>
+  <si>
+    <t>Completed Section 5 (Overall Management Assessment) which had headers but no data. Resized all columns. Added text wrapping and row heights.</t>
+  </si>
+  <si>
+    <t>Section 5 now has 7 assessment categories + overall summary row: Executive Leadership (★★★★☆), Board Independence (★★★☆☆), Technical Expertise (★★★★★), Strategic Relationships (★★★★★), Compensation Alignment (★★★★★), Insider Conviction (★★★★★), Operational Readiness (★★★☆☆), OVERALL (★★★★☆). Each row has Strengths, Weaknesses/Risks, and Rating. Column widths: A=180, B=200, C=280, D=250, E=200, F=230, G=100, H=320pt.</t>
+  </si>
+  <si>
+    <t>Management &amp; Governance sheet now fully complete (A1:H55). All 5 sections populated with data. Text wrapping enabled. Column widths optimized for content.</t>
   </si>
 </sst>
 </file>
@@ -3587,7 +5977,7 @@
     <numFmt numFmtId="173" formatCode="\+0%;\-0%"/>
     <numFmt numFmtId="174" formatCode="&quot;$&quot;#,##0,,&quot;M&quot;"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3913,8 +6303,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4005,6 +6426,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6DCE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4018,7 +6445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4250,6 +6677,57 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4620,22 +7098,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -4645,45 +7123,45 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="17" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B11" s="22">
         <v>7496238</v>
@@ -4703,7 +7181,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B12" s="22">
         <v>25000</v>
@@ -4723,7 +7201,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B13" s="22">
         <v>411438</v>
@@ -4743,7 +7221,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B14" s="22">
         <v>0</v>
@@ -4763,7 +7241,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B15" s="22">
         <v>399095</v>
@@ -4783,7 +7261,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B16" s="22">
         <v>640687</v>
@@ -4803,7 +7281,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B17" s="23">
         <f>SUM(B11:B16)</f>
@@ -4828,12 +7306,12 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B20" s="22">
         <v>132988</v>
@@ -4853,7 +7331,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B21" s="22">
         <v>332578</v>
@@ -4873,7 +7351,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B22" s="22">
         <v>3557734</v>
@@ -4893,7 +7371,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B23" s="22">
         <v>0</v>
@@ -4913,7 +7391,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B24" s="23">
         <f>SUM(B20:B23)</f>
@@ -4938,7 +7416,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="24" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B26" s="25">
         <f>B17+B24</f>
@@ -4963,17 +7441,17 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="20" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="21" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B30" s="22">
         <v>2532332</v>
@@ -4993,7 +7471,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B31" s="22">
         <v>0</v>
@@ -5013,7 +7491,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B32" s="22">
         <v>1151052</v>
@@ -5033,7 +7511,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B33" s="22">
         <v>0</v>
@@ -5053,7 +7531,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="24" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B34" s="25">
         <f>SUM(B30:B33)</f>
@@ -5078,12 +7556,12 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B37" s="22">
         <v>26342634</v>
@@ -5103,7 +7581,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B38" s="22">
         <v>4917414</v>
@@ -5123,7 +7601,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B39" s="22">
         <v>0</v>
@@ -5143,7 +7621,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B40" s="26">
         <v>-21947674</v>
@@ -5163,7 +7641,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="24" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B41" s="25">
         <f>SUM(B37:B40)</f>
@@ -5188,7 +7666,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B43" s="28">
         <f>B34+B41</f>
@@ -5213,7 +7691,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="30" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B44" s="31">
         <f>B26-B43</f>
@@ -5258,7 +7736,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -5268,40 +7746,40 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B49" s="17" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A50" s="18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="20" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B52" s="22">
         <v>-3520097</v>
@@ -5321,7 +7799,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B53" s="22">
         <v>-1646973</v>
@@ -5341,7 +7819,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B54" s="22">
         <v>-996483</v>
@@ -5361,7 +7839,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B55" s="22">
         <v>-854242</v>
@@ -5381,7 +7859,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B56" s="22">
         <v>-826528</v>
@@ -5401,7 +7879,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B57" s="22">
         <v>-184735</v>
@@ -5421,7 +7899,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B58" s="22">
         <v>-177714</v>
@@ -5441,7 +7919,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B59" s="22">
         <v>-392400</v>
@@ -5461,7 +7939,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B60" s="23">
         <f>SUM(B52:B59)</f>
@@ -5486,12 +7964,12 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="20" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B63" s="22">
         <v>57712</v>
@@ -5511,7 +7989,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B64" s="22">
         <v>-66515</v>
@@ -5531,7 +8009,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B65" s="22">
         <v>383218</v>
@@ -5551,7 +8029,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B66" s="22">
         <v>-67711</v>
@@ -5571,7 +8049,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B67" s="23">
         <f>SUM(B63:B66)</f>
@@ -5596,7 +8074,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="33" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B69" s="34">
         <f>B60+B67</f>
@@ -5621,7 +8099,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B71" s="35">
         <v>-0.15</v>
@@ -5641,7 +8119,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B72" s="32">
         <v>55236302</v>
@@ -5661,7 +8139,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="36" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F73" s="37">
         <f>D69+E69+F69</f>
@@ -5670,7 +8148,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="15" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
@@ -5680,40 +8158,40 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B77" s="17" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A78" s="18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="20" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B80" s="22">
         <v>-8292468</v>
@@ -5733,12 +8211,12 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B82" s="22">
         <v>1646973</v>
@@ -5758,7 +8236,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B83" s="22">
         <v>66515</v>
@@ -5778,7 +8256,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B84" s="22">
         <v>-383219</v>
@@ -5798,7 +8276,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B85" s="22">
         <v>59397</v>
@@ -5818,12 +8296,12 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B87" s="22">
         <v>-450821</v>
@@ -5843,7 +8321,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B88" s="22">
         <v>3648873</v>
@@ -5863,7 +8341,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="38" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B89" s="39">
         <v>-3704750</v>
@@ -5883,12 +8361,12 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="20" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B92" s="22">
         <v>10562627</v>
@@ -5908,7 +8386,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B93" s="22">
         <v>18132</v>
@@ -5928,7 +8406,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B94" s="22">
         <v>-560089</v>
@@ -5948,7 +8426,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="40" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B95" s="41">
         <f>SUM(B92:B94)</f>
@@ -5973,7 +8451,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="20" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B97" s="23">
         <f>B89+B95</f>
@@ -5998,7 +8476,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B98" s="22">
         <v>1180318</v>
@@ -6018,7 +8496,7 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="27" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B99" s="28">
         <f>B97+B98</f>
@@ -6043,7 +8521,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="30" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B100" s="31">
         <f>B99-B11</f>
@@ -6068,7 +8546,7 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="15" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B102" s="16"/>
       <c r="C102" s="16"/>
@@ -6078,7 +8556,7 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B103" s="42">
         <f>B41/B45</f>
@@ -6103,7 +8581,7 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B104" s="22">
         <f>B17-B34</f>
@@ -6128,7 +8606,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B105" s="43">
         <f>B17/B34</f>
@@ -6153,7 +8631,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B106" s="43">
         <f>B34/B41</f>
@@ -6178,7 +8656,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B107" s="44">
         <f>B11/B26</f>
@@ -6203,7 +8681,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B108" s="22">
         <f>B89/4</f>
@@ -6228,7 +8706,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B109" s="22">
         <f>B89</f>
@@ -6253,7 +8731,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B110" s="45">
         <f>IF(B89=0,"N/A",-B11/B108*12)</f>
@@ -6293,22 +8771,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -6321,33 +8799,33 @@
     </row>
     <row r="6" spans="1:9" ht="28" x14ac:dyDescent="0.2">
       <c r="B6" s="19" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B7" s="22">
         <v>-3764747</v>
@@ -6376,7 +8854,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B8" s="47">
         <v>7496238</v>
@@ -6434,7 +8912,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C10" s="44">
         <f>(C9-B9)/B9</f>
@@ -6467,7 +8945,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C11" s="44">
         <f>C9/$B9-1</f>
@@ -6500,7 +8978,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C12" s="22">
         <v>0</v>
@@ -6526,7 +9004,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="48" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B14" s="49"/>
       <c r="C14" s="49"/>
@@ -6539,33 +9017,33 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="18" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C15" s="18" t="s">
         <v>23</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C16" s="51">
         <v>32600000</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F16" s="51">
         <v>3200000</v>
@@ -6581,13 +9059,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C17" s="47">
         <v>14663500</v>
       </c>
       <c r="E17" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F17" s="51">
         <v>2500000</v>
@@ -6603,13 +9081,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C18" s="32">
         <v>192400000</v>
       </c>
       <c r="E18" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F18" s="51">
         <v>4500000</v>
@@ -6625,7 +9103,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="53" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B21" s="54"/>
       <c r="C21" s="54"/>
@@ -6638,24 +9116,24 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E22" s="57" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B23" s="47">
         <v>2664000</v>
@@ -6667,12 +9145,12 @@
         <v>9965600</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B24" s="47">
         <v>165000</v>
@@ -6684,12 +9162,12 @@
         <v>461000</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B25" s="47">
         <v>91400</v>
@@ -6701,12 +9179,12 @@
         <v>1980000</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B26" s="47">
         <v>353000</v>
@@ -6718,12 +9196,12 @@
         <v>2256900</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B27" s="59">
         <f>SUM(B23:B26)</f>
@@ -6740,21 +9218,21 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="60" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B28" s="61" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D28" s="61" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="62" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B31" s="63"/>
       <c r="C31" s="63"/>
@@ -6767,7 +9245,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C32" s="64" t="s">
         <v>22</v>
@@ -6778,40 +9256,40 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C33" s="47">
         <v>675000000</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C34" s="47">
         <v>240000000</v>
       </c>
       <c r="D34" s="55" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C35" s="47">
         <v>90000000</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C36" s="65">
         <f>SUM(C33:C35)</f>
@@ -6820,7 +9298,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C38" s="47">
         <v>32600000</v>
@@ -6828,7 +9306,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C39" s="66">
         <v>-21400000</v>
@@ -6836,7 +9314,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C40" s="23">
         <f>C38+C39</f>
@@ -6845,14 +9323,14 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="33" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C41" s="34">
         <f>C40-C36</f>
         <v>-993800000</v>
       </c>
       <c r="D41" s="68" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -6872,7 +9350,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="101" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -6886,12 +9364,12 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="103" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="104" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -6908,23 +9386,23 @@
         <v>5</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E5" s="19"/>
       <c r="F5" s="106" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="G5" s="107" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" s="107" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" s="54"/>
       <c r="J5" s="54"/>
@@ -6934,29 +9412,29 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C6" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="108" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H6" s="108" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I6" s="108"/>
       <c r="J6" s="108" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -6964,77 +9442,77 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H7" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B8" s="109" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D8" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E8" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B9" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C9" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D9" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E9" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F9" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G9" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H9" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -7042,28 +9520,28 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D10" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E10" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G10" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H10" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J10" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -7071,7 +9549,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C11" s="7">
         <v>0</v>
@@ -7080,39 +9558,39 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="H11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B12" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C12" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="H12" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -7120,10 +9598,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="70" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C13" s="70" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D13" s="70"/>
       <c r="E13" s="70"/>
@@ -7131,106 +9609,106 @@
         <v>15</v>
       </c>
       <c r="G13" s="70" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H13" s="70" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I13" s="70"/>
       <c r="J13" s="70" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B14" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C14" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="H14" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C15" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="G15" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C16" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D16" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C17" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D17" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -7238,21 +9716,21 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C18" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="71" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B19" s="72" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D19" s="72"/>
       <c r="E19" s="72"/>
@@ -7262,7 +9740,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B20" s="110">
         <v>1.93</v>
@@ -7271,13 +9749,13 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -7291,33 +9769,33 @@
         <v>0.187</v>
       </c>
       <c r="D21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B22" s="54" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22" s="54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F22" s="54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G22" s="54"/>
       <c r="H22" s="54"/>
@@ -7326,22 +9804,22 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B23" s="111" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D23" s="54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23" s="54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F23" s="54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
@@ -7353,62 +9831,62 @@
         <v>5</v>
       </c>
       <c r="B24" s="82" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C24" s="82" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D24" s="82" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>5</v>
       </c>
       <c r="G24" s="82" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="H24" s="82" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C25" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D25" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H25" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="74" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B26" s="75" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C26" s="75" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D26" s="112" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E26" s="75"/>
       <c r="F26" s="75" t="s">
@@ -7423,25 +9901,25 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B27">
         <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H27" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -7449,22 +9927,22 @@
         <v>30</v>
       </c>
       <c r="B28" s="109" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G28" s="109" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H28" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -7472,119 +9950,119 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C29" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D29" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G29" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H29" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B30" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C30" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D30" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F30" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G30" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H30" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B31" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C31" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D31" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F31" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G31" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H31" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B32" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C32" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D32" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F32" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="G32" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H32" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C33" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D33" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F33" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G33" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H33" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="104" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B35" s="54"/>
       <c r="C35" s="54"/>
@@ -7601,96 +10079,96 @@
         <v>5</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C36" s="82" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D36" s="82" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E36" s="82" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F36" s="82" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G36" s="82" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C37" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G37" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B38" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C38" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G38" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B39" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C39" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D39" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E39" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F39" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="G39" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B40" s="9">
         <v>0.33</v>
@@ -7699,44 +10177,44 @@
         <v>0.187</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G40" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G41" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="76" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -7750,37 +10228,37 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="115" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="123" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -7794,7 +10272,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="102" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -7802,20 +10280,20 @@
         <v>5</v>
       </c>
       <c r="B54" s="108" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C54" s="108" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D54" s="108" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="E54" s="108" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="F54" s="116"/>
       <c r="G54" s="108" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="H54" s="116"/>
       <c r="I54" s="116"/>
@@ -7823,22 +10301,22 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B55" s="109" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
@@ -7846,19 +10324,19 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C56" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D56" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E56" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="G56" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
@@ -7866,19 +10344,19 @@
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C57" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D57" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E57" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="G57" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
@@ -7900,33 +10378,33 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B59" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C59" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D59" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E59" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="G59" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B60" s="110">
         <v>0.33</v>
       </c>
       <c r="C60" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D60" s="8">
         <v>0.18099999999999999</v>
@@ -7935,27 +10413,27 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="G60" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C61" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D61" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="E61" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="G61" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
@@ -7963,39 +10441,39 @@
         <v>19</v>
       </c>
       <c r="B62" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C62" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D62" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E62" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="G62" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B63" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C63" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D63" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E63" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="G63" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
@@ -8003,58 +10481,58 @@
         <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C64" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D64" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E64" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="G64" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B65" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C65" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D65" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E65" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B66" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C66" s="124" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D66" s="125" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="E66" s="125" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B68" s="54"/>
       <c r="C68" s="54"/>
@@ -8068,22 +10546,22 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -8103,24 +10581,24 @@
   <sheetData>
     <row r="1" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="76" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B5" s="77">
         <v>1590000000</v>
@@ -8128,7 +10606,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B6" s="3">
         <v>1.05</v>
@@ -8136,7 +10614,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B7" s="78">
         <v>173267217</v>
@@ -8144,7 +10622,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B8" s="78">
         <v>192400000</v>
@@ -8152,7 +10630,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B9" s="67">
         <f>B6*B7</f>
@@ -8161,7 +10639,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B10" s="67">
         <f>B6*B8</f>
@@ -8170,7 +10648,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B11" s="79">
         <f>B9/B5</f>
@@ -8179,7 +10657,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B12" s="79">
         <f>B10/B5</f>
@@ -8188,7 +10666,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="80" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B14" s="81"/>
       <c r="C14" s="81"/>
@@ -8201,7 +10679,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" s="83">
         <v>0.03</v>
@@ -8230,7 +10708,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B16" s="85">
         <f>$B$5*B15</f>
@@ -8267,7 +10745,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B17" s="87">
         <f>$B$5*B15/$B$7</f>
@@ -8304,7 +10782,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B18" s="87">
         <f>$B$5*B15/$B$8</f>
@@ -8341,7 +10819,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B19" s="90">
         <f>B17/$B$6-1</f>
@@ -8378,36 +10856,36 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B20" s="92" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C20" s="93" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D20" s="89" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E20" s="94" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F20" s="95" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="G20" s="96" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H20" s="96" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I20" s="96" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="97" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B22" s="49"/>
       <c r="C22" s="49"/>
@@ -8417,27 +10895,27 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B23" s="82" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C23" s="82" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D23" s="82" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F23" s="82" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B24" s="98">
         <v>0.03</v>
@@ -8455,12 +10933,12 @@
         <v>-0.73781207885060318</v>
       </c>
       <c r="F24" s="55" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B25" s="98">
         <v>0.11</v>
@@ -8478,12 +10956,12 @@
         <v>-3.8644289118878294E-2</v>
       </c>
       <c r="F25" s="55" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B26" s="98">
         <v>0.2</v>
@@ -8501,12 +10979,12 @@
         <v>0.74791947432931205</v>
       </c>
       <c r="F26" s="55" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B27" s="98">
         <v>0.35</v>
@@ -8524,17 +11002,17 @@
         <v>2.0588590800762963</v>
       </c>
       <c r="F27" s="55" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="100" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="100" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -8556,7 +11034,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="101" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B1" s="105"/>
       <c r="C1" s="105"/>
@@ -8566,12 +11044,12 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="103" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B4" s="54"/>
       <c r="C4" s="54"/>
@@ -8581,12 +11059,12 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B7" s="54"/>
       <c r="C7" s="54"/>
@@ -8596,227 +11074,227 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B9" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C9" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="D9" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="E9" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F9" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B10" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="C10" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D10" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="E10" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F10" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B11" t="s">
+        <v>621</v>
+      </c>
+      <c r="C11" t="s">
+        <v>622</v>
+      </c>
+      <c r="D11" t="s">
+        <v>623</v>
+      </c>
+      <c r="E11" t="s">
+        <v>615</v>
+      </c>
+      <c r="F11" t="s">
         <v>616</v>
-      </c>
-      <c r="C11" t="s">
-        <v>617</v>
-      </c>
-      <c r="D11" t="s">
-        <v>618</v>
-      </c>
-      <c r="E11" t="s">
-        <v>610</v>
-      </c>
-      <c r="F11" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B12" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C12" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="D12" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E12" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F12" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B13" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="C13" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="D13" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E13" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="B14" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="C14" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="D14" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="E14" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B15" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C15" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="D15" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E15" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F15" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B16" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C16" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="D16" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="E16" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F16" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B17" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="C17" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="D17" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="E17" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F17" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B18" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C18" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="D18" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E18" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B20" s="54"/>
       <c r="C20" s="54"/>
@@ -8826,110 +11304,110 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="F21" s="116"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B22" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="C22" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D22" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E22" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B23" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C23" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D23" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="E23" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B24" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="C24" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D24" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="E24" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B25" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C25" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D25" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="E25" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B26" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C26" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="D26" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="E26" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -8939,46 +11417,46 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="18" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E29" s="116"/>
       <c r="F29" s="116"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B30" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="C30" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="D30" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B31" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="C31" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="D31" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -8986,60 +11464,60 @@
         <v>2026</v>
       </c>
       <c r="B32" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C32" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D32" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B33" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C33" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="D33" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="B34" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="C34" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="D34" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B35" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C35" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="D35" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="B37" s="54"/>
       <c r="C37" s="54"/>
@@ -9052,104 +11530,104 @@
         <v>5</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="E38" s="116"/>
       <c r="F38" s="116"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="B39" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C39" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="D39" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="B40" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="C40" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="D40" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="B41" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C41" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="D41" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="B42" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C42" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="D42" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="B43" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="C43" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="D43" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="B44" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="C44" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="D44" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -9159,22 +11637,22 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="30" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -9183,6 +11661,1083 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B8A62D-F775-BD48-B9AE-19BD63E1EBE0}">
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" customWidth="1"/>
+    <col min="6" max="6" width="38.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="53.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="126" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="128" t="s">
+        <v>744</v>
+      </c>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+    </row>
+    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="129" t="s">
+        <v>745</v>
+      </c>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="127"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="127"/>
+    </row>
+    <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="130" t="s">
+        <v>746</v>
+      </c>
+      <c r="B5" s="131"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="131"/>
+    </row>
+    <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="132" t="s">
+        <v>747</v>
+      </c>
+      <c r="B6" s="132" t="s">
+        <v>748</v>
+      </c>
+      <c r="C6" s="132" t="s">
+        <v>749</v>
+      </c>
+      <c r="D6" s="132" t="s">
+        <v>750</v>
+      </c>
+      <c r="E6" s="132" t="s">
+        <v>751</v>
+      </c>
+      <c r="F6" s="132" t="s">
+        <v>752</v>
+      </c>
+      <c r="G6" s="132" t="s">
+        <v>753</v>
+      </c>
+      <c r="H6" s="132" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="133" t="s">
+        <v>754</v>
+      </c>
+      <c r="B7" s="127" t="s">
+        <v>755</v>
+      </c>
+      <c r="C7" s="127" t="s">
+        <v>756</v>
+      </c>
+      <c r="D7" s="127" t="s">
+        <v>757</v>
+      </c>
+      <c r="E7" s="127" t="s">
+        <v>758</v>
+      </c>
+      <c r="F7" s="127" t="s">
+        <v>759</v>
+      </c>
+      <c r="G7" s="127" t="s">
+        <v>760</v>
+      </c>
+      <c r="H7" s="127" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="133" t="s">
+        <v>762</v>
+      </c>
+      <c r="B8" s="127" t="s">
+        <v>763</v>
+      </c>
+      <c r="C8" s="127" t="s">
+        <v>764</v>
+      </c>
+      <c r="D8" s="127" t="s">
+        <v>765</v>
+      </c>
+      <c r="E8" s="127" t="s">
+        <v>766</v>
+      </c>
+      <c r="F8" s="127" t="s">
+        <v>767</v>
+      </c>
+      <c r="G8" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="127" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="133" t="s">
+        <v>769</v>
+      </c>
+      <c r="B9" s="127" t="s">
+        <v>770</v>
+      </c>
+      <c r="C9" s="127" t="s">
+        <v>771</v>
+      </c>
+      <c r="D9" s="127" t="s">
+        <v>772</v>
+      </c>
+      <c r="E9" s="127" t="s">
+        <v>773</v>
+      </c>
+      <c r="F9" s="127" t="s">
+        <v>774</v>
+      </c>
+      <c r="G9" s="127" t="s">
+        <v>775</v>
+      </c>
+      <c r="H9" s="127" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="133" t="s">
+        <v>777</v>
+      </c>
+      <c r="B10" s="127" t="s">
+        <v>778</v>
+      </c>
+      <c r="C10" s="127" t="s">
+        <v>779</v>
+      </c>
+      <c r="D10" s="127" t="s">
+        <v>780</v>
+      </c>
+      <c r="E10" s="127" t="s">
+        <v>781</v>
+      </c>
+      <c r="F10" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="127" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="133" t="s">
+        <v>783</v>
+      </c>
+      <c r="B11" s="127" t="s">
+        <v>784</v>
+      </c>
+      <c r="C11" s="127" t="s">
+        <v>785</v>
+      </c>
+      <c r="D11" s="127" t="s">
+        <v>786</v>
+      </c>
+      <c r="E11" s="127" t="s">
+        <v>787</v>
+      </c>
+      <c r="F11" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="127" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="133" t="s">
+        <v>789</v>
+      </c>
+      <c r="B12" s="127" t="s">
+        <v>790</v>
+      </c>
+      <c r="C12" s="127" t="s">
+        <v>791</v>
+      </c>
+      <c r="D12" s="127" t="s">
+        <v>792</v>
+      </c>
+      <c r="E12" s="127" t="s">
+        <v>793</v>
+      </c>
+      <c r="F12" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="127" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="133" t="s">
+        <v>795</v>
+      </c>
+      <c r="B13" s="127" t="s">
+        <v>796</v>
+      </c>
+      <c r="C13" s="127" t="s">
+        <v>797</v>
+      </c>
+      <c r="D13" s="127" t="s">
+        <v>798</v>
+      </c>
+      <c r="E13" s="127" t="s">
+        <v>799</v>
+      </c>
+      <c r="F13" s="127" t="s">
+        <v>800</v>
+      </c>
+      <c r="G13" s="127" t="s">
+        <v>801</v>
+      </c>
+      <c r="H13" s="127" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="127"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+    </row>
+    <row r="15" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="130" t="s">
+        <v>803</v>
+      </c>
+      <c r="B15" s="131"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+    </row>
+    <row r="16" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="132" t="s">
+        <v>747</v>
+      </c>
+      <c r="B16" s="132" t="s">
+        <v>804</v>
+      </c>
+      <c r="C16" s="132" t="s">
+        <v>749</v>
+      </c>
+      <c r="D16" s="132" t="s">
+        <v>805</v>
+      </c>
+      <c r="E16" s="132" t="s">
+        <v>806</v>
+      </c>
+      <c r="F16" s="132" t="s">
+        <v>807</v>
+      </c>
+      <c r="G16" s="132" t="s">
+        <v>808</v>
+      </c>
+      <c r="H16" s="132" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="133" t="s">
+        <v>809</v>
+      </c>
+      <c r="B17" s="127" t="s">
+        <v>810</v>
+      </c>
+      <c r="C17" s="127" t="s">
+        <v>811</v>
+      </c>
+      <c r="D17" s="127" t="s">
+        <v>812</v>
+      </c>
+      <c r="E17" s="134">
+        <v>44835</v>
+      </c>
+      <c r="F17" s="127" t="s">
+        <v>813</v>
+      </c>
+      <c r="G17" s="127" t="s">
+        <v>814</v>
+      </c>
+      <c r="H17" s="127" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="133" t="s">
+        <v>816</v>
+      </c>
+      <c r="B18" s="127" t="s">
+        <v>817</v>
+      </c>
+      <c r="C18" s="127" t="s">
+        <v>818</v>
+      </c>
+      <c r="D18" s="127" t="s">
+        <v>819</v>
+      </c>
+      <c r="E18" s="127" t="s">
+        <v>820</v>
+      </c>
+      <c r="F18" s="127" t="s">
+        <v>821</v>
+      </c>
+      <c r="G18" s="127" t="s">
+        <v>814</v>
+      </c>
+      <c r="H18" s="127" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="133" t="s">
+        <v>823</v>
+      </c>
+      <c r="B19" s="127" t="s">
+        <v>824</v>
+      </c>
+      <c r="C19" s="127" t="s">
+        <v>825</v>
+      </c>
+      <c r="D19" s="127" t="s">
+        <v>826</v>
+      </c>
+      <c r="E19" s="134">
+        <v>45383</v>
+      </c>
+      <c r="F19" s="127" t="s">
+        <v>827</v>
+      </c>
+      <c r="G19" s="127" t="s">
+        <v>814</v>
+      </c>
+      <c r="H19" s="127" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="133" t="s">
+        <v>829</v>
+      </c>
+      <c r="B20" s="127" t="s">
+        <v>830</v>
+      </c>
+      <c r="C20" s="127" t="s">
+        <v>831</v>
+      </c>
+      <c r="D20" s="127" t="s">
+        <v>832</v>
+      </c>
+      <c r="E20" s="127" t="s">
+        <v>820</v>
+      </c>
+      <c r="F20" s="127" t="s">
+        <v>833</v>
+      </c>
+      <c r="G20" s="127" t="s">
+        <v>834</v>
+      </c>
+      <c r="H20" s="127" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="133" t="s">
+        <v>836</v>
+      </c>
+      <c r="B21" s="127" t="s">
+        <v>837</v>
+      </c>
+      <c r="C21" s="127" t="s">
+        <v>838</v>
+      </c>
+      <c r="D21" s="127" t="s">
+        <v>839</v>
+      </c>
+      <c r="E21" s="127" t="s">
+        <v>820</v>
+      </c>
+      <c r="F21" s="127" t="s">
+        <v>840</v>
+      </c>
+      <c r="G21" s="127" t="s">
+        <v>834</v>
+      </c>
+      <c r="H21" s="127" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="133" t="s">
+        <v>842</v>
+      </c>
+      <c r="B22" s="127" t="s">
+        <v>843</v>
+      </c>
+      <c r="C22" s="127" t="s">
+        <v>844</v>
+      </c>
+      <c r="D22" s="127" t="s">
+        <v>845</v>
+      </c>
+      <c r="E22" s="127" t="s">
+        <v>820</v>
+      </c>
+      <c r="F22" s="127" t="s">
+        <v>846</v>
+      </c>
+      <c r="G22" s="127" t="s">
+        <v>834</v>
+      </c>
+      <c r="H22" s="127" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="133" t="s">
+        <v>848</v>
+      </c>
+      <c r="B23" s="127" t="s">
+        <v>849</v>
+      </c>
+      <c r="C23" s="127" t="s">
+        <v>850</v>
+      </c>
+      <c r="D23" s="127" t="s">
+        <v>851</v>
+      </c>
+      <c r="E23" s="127" t="s">
+        <v>852</v>
+      </c>
+      <c r="F23" s="127" t="s">
+        <v>853</v>
+      </c>
+      <c r="G23" s="127" t="s">
+        <v>814</v>
+      </c>
+      <c r="H23" s="127" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="127"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="127"/>
+    </row>
+    <row r="25" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="130" t="s">
+        <v>855</v>
+      </c>
+      <c r="B25" s="131"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="131"/>
+    </row>
+    <row r="26" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="132" t="s">
+        <v>747</v>
+      </c>
+      <c r="B26" s="132" t="s">
+        <v>856</v>
+      </c>
+      <c r="C26" s="132" t="s">
+        <v>749</v>
+      </c>
+      <c r="D26" s="132" t="s">
+        <v>805</v>
+      </c>
+      <c r="E26" s="132" t="s">
+        <v>857</v>
+      </c>
+      <c r="F26" s="132" t="s">
+        <v>858</v>
+      </c>
+      <c r="G26" s="135"/>
+      <c r="H26" s="132" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="133" t="s">
+        <v>859</v>
+      </c>
+      <c r="B27" s="127" t="s">
+        <v>860</v>
+      </c>
+      <c r="C27" s="127" t="s">
+        <v>861</v>
+      </c>
+      <c r="D27" s="127" t="s">
+        <v>862</v>
+      </c>
+      <c r="E27" s="127" t="s">
+        <v>863</v>
+      </c>
+      <c r="F27" s="127" t="s">
+        <v>864</v>
+      </c>
+      <c r="G27" s="127"/>
+      <c r="H27" s="127" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="133" t="s">
+        <v>866</v>
+      </c>
+      <c r="B28" s="127" t="s">
+        <v>867</v>
+      </c>
+      <c r="C28" s="127" t="s">
+        <v>868</v>
+      </c>
+      <c r="D28" s="127" t="s">
+        <v>869</v>
+      </c>
+      <c r="E28" s="127" t="s">
+        <v>863</v>
+      </c>
+      <c r="F28" s="127" t="s">
+        <v>870</v>
+      </c>
+      <c r="G28" s="127"/>
+      <c r="H28" s="127" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="133" t="s">
+        <v>872</v>
+      </c>
+      <c r="B29" s="127" t="s">
+        <v>873</v>
+      </c>
+      <c r="C29" s="127" t="s">
+        <v>874</v>
+      </c>
+      <c r="D29" s="127" t="s">
+        <v>875</v>
+      </c>
+      <c r="E29" s="127" t="s">
+        <v>863</v>
+      </c>
+      <c r="F29" s="127" t="s">
+        <v>876</v>
+      </c>
+      <c r="G29" s="127"/>
+      <c r="H29" s="127" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="133" t="s">
+        <v>878</v>
+      </c>
+      <c r="B30" s="127" t="s">
+        <v>879</v>
+      </c>
+      <c r="C30" s="127" t="s">
+        <v>880</v>
+      </c>
+      <c r="D30" s="127" t="s">
+        <v>881</v>
+      </c>
+      <c r="E30" s="127" t="s">
+        <v>882</v>
+      </c>
+      <c r="F30" s="127" t="s">
+        <v>883</v>
+      </c>
+      <c r="G30" s="127"/>
+      <c r="H30" s="127" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="133" t="s">
+        <v>885</v>
+      </c>
+      <c r="B31" s="127" t="s">
+        <v>886</v>
+      </c>
+      <c r="C31" s="127" t="s">
+        <v>887</v>
+      </c>
+      <c r="D31" s="127" t="s">
+        <v>888</v>
+      </c>
+      <c r="E31" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="127" t="s">
+        <v>889</v>
+      </c>
+      <c r="G31" s="127"/>
+      <c r="H31" s="127" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="133" t="s">
+        <v>891</v>
+      </c>
+      <c r="B32" s="127" t="s">
+        <v>892</v>
+      </c>
+      <c r="C32" s="127" t="s">
+        <v>893</v>
+      </c>
+      <c r="D32" s="127" t="s">
+        <v>894</v>
+      </c>
+      <c r="E32" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="127" t="s">
+        <v>895</v>
+      </c>
+      <c r="G32" s="127"/>
+      <c r="H32" s="127" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="127"/>
+      <c r="B33" s="127"/>
+      <c r="C33" s="127"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="127"/>
+      <c r="G33" s="127"/>
+      <c r="H33" s="127"/>
+    </row>
+    <row r="34" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="130" t="s">
+        <v>897</v>
+      </c>
+      <c r="B34" s="131"/>
+      <c r="C34" s="131"/>
+      <c r="D34" s="131"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="127"/>
+      <c r="B35" s="127"/>
+      <c r="C35" s="127"/>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+    </row>
+    <row r="36" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="132" t="s">
+        <v>898</v>
+      </c>
+      <c r="B36" s="132" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="132" t="s">
+        <v>899</v>
+      </c>
+      <c r="D36" s="132" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="127"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="127"/>
+      <c r="H36" s="127"/>
+    </row>
+    <row r="37" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="136" t="s">
+        <v>900</v>
+      </c>
+      <c r="B37" s="127" t="s">
+        <v>901</v>
+      </c>
+      <c r="C37" s="137" t="s">
+        <v>902</v>
+      </c>
+      <c r="D37" s="127" t="s">
+        <v>814</v>
+      </c>
+      <c r="E37" s="127"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="127"/>
+      <c r="H37" s="127"/>
+    </row>
+    <row r="38" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="136" t="s">
+        <v>903</v>
+      </c>
+      <c r="B38" s="127" t="s">
+        <v>904</v>
+      </c>
+      <c r="C38" s="137" t="s">
+        <v>905</v>
+      </c>
+      <c r="D38" s="127" t="s">
+        <v>814</v>
+      </c>
+      <c r="E38" s="127"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="127"/>
+    </row>
+    <row r="39" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="136" t="s">
+        <v>906</v>
+      </c>
+      <c r="B39" s="127" t="s">
+        <v>907</v>
+      </c>
+      <c r="C39" s="137" t="s">
+        <v>908</v>
+      </c>
+      <c r="D39" s="127" t="s">
+        <v>834</v>
+      </c>
+      <c r="E39" s="127"/>
+      <c r="F39" s="127"/>
+      <c r="G39" s="127"/>
+      <c r="H39" s="127"/>
+    </row>
+    <row r="40" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="136" t="s">
+        <v>909</v>
+      </c>
+      <c r="B40" s="127" t="s">
+        <v>910</v>
+      </c>
+      <c r="C40" s="138" t="s">
+        <v>911</v>
+      </c>
+      <c r="D40" s="127" t="s">
+        <v>912</v>
+      </c>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="127"/>
+      <c r="H40" s="127"/>
+    </row>
+    <row r="41" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="136" t="s">
+        <v>913</v>
+      </c>
+      <c r="B41" s="127" t="s">
+        <v>914</v>
+      </c>
+      <c r="C41" s="137" t="s">
+        <v>915</v>
+      </c>
+      <c r="D41" s="127" t="s">
+        <v>834</v>
+      </c>
+      <c r="E41" s="127"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+    </row>
+    <row r="42" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="136" t="s">
+        <v>916</v>
+      </c>
+      <c r="B42" s="127" t="s">
+        <v>917</v>
+      </c>
+      <c r="C42" s="139" t="s">
+        <v>918</v>
+      </c>
+      <c r="D42" s="127" t="s">
+        <v>814</v>
+      </c>
+      <c r="E42" s="127"/>
+      <c r="F42" s="127"/>
+      <c r="G42" s="127"/>
+      <c r="H42" s="127"/>
+    </row>
+    <row r="43" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="136" t="s">
+        <v>919</v>
+      </c>
+      <c r="B43" s="127" t="s">
+        <v>920</v>
+      </c>
+      <c r="C43" s="137" t="s">
+        <v>921</v>
+      </c>
+      <c r="D43" s="127" t="s">
+        <v>814</v>
+      </c>
+      <c r="E43" s="127"/>
+      <c r="F43" s="127"/>
+      <c r="G43" s="127"/>
+      <c r="H43" s="127"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="127"/>
+      <c r="B44" s="127"/>
+      <c r="C44" s="127"/>
+      <c r="D44" s="127"/>
+      <c r="E44" s="127"/>
+      <c r="F44" s="127"/>
+      <c r="G44" s="127"/>
+      <c r="H44" s="127"/>
+    </row>
+    <row r="45" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="130" t="s">
+        <v>922</v>
+      </c>
+      <c r="B45" s="131"/>
+      <c r="C45" s="131"/>
+      <c r="D45" s="131"/>
+      <c r="E45" s="131"/>
+      <c r="F45" s="131"/>
+      <c r="G45" s="131"/>
+      <c r="H45" s="131"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="127"/>
+      <c r="B46" s="127"/>
+      <c r="C46" s="127"/>
+      <c r="D46" s="127"/>
+      <c r="E46" s="127"/>
+      <c r="F46" s="127"/>
+      <c r="G46" s="127"/>
+      <c r="H46" s="127"/>
+    </row>
+    <row r="47" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="132" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="132" t="s">
+        <v>923</v>
+      </c>
+      <c r="C47" s="132" t="s">
+        <v>924</v>
+      </c>
+      <c r="D47" s="132" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="127"/>
+      <c r="F47" s="127"/>
+      <c r="G47" s="127"/>
+      <c r="H47" s="127"/>
+    </row>
+    <row r="48" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="133" t="s">
+        <v>925</v>
+      </c>
+      <c r="B48" s="136" t="s">
+        <v>926</v>
+      </c>
+      <c r="C48" s="136" t="s">
+        <v>927</v>
+      </c>
+      <c r="D48" s="140" t="s">
+        <v>834</v>
+      </c>
+      <c r="E48" s="127"/>
+      <c r="F48" s="127"/>
+      <c r="G48" s="127"/>
+      <c r="H48" s="127"/>
+    </row>
+    <row r="49" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="133" t="s">
+        <v>928</v>
+      </c>
+      <c r="B49" s="136" t="s">
+        <v>929</v>
+      </c>
+      <c r="C49" s="136" t="s">
+        <v>930</v>
+      </c>
+      <c r="D49" s="140" t="s">
+        <v>912</v>
+      </c>
+      <c r="E49" s="127"/>
+      <c r="F49" s="127"/>
+      <c r="G49" s="127"/>
+      <c r="H49" s="127"/>
+    </row>
+    <row r="50" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="133" t="s">
+        <v>931</v>
+      </c>
+      <c r="B50" s="136" t="s">
+        <v>932</v>
+      </c>
+      <c r="C50" s="136" t="s">
+        <v>933</v>
+      </c>
+      <c r="D50" s="140" t="s">
+        <v>814</v>
+      </c>
+      <c r="E50" s="127"/>
+      <c r="F50" s="127"/>
+      <c r="G50" s="127"/>
+      <c r="H50" s="127"/>
+    </row>
+    <row r="51" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="133" t="s">
+        <v>934</v>
+      </c>
+      <c r="B51" s="136" t="s">
+        <v>935</v>
+      </c>
+      <c r="C51" s="136" t="s">
+        <v>936</v>
+      </c>
+      <c r="D51" s="140" t="s">
+        <v>814</v>
+      </c>
+      <c r="E51" s="127"/>
+      <c r="F51" s="127"/>
+      <c r="G51" s="127"/>
+      <c r="H51" s="127"/>
+    </row>
+    <row r="52" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="133" t="s">
+        <v>937</v>
+      </c>
+      <c r="B52" s="136" t="s">
+        <v>938</v>
+      </c>
+      <c r="C52" s="136" t="s">
+        <v>939</v>
+      </c>
+      <c r="D52" s="140" t="s">
+        <v>814</v>
+      </c>
+      <c r="E52" s="127"/>
+      <c r="F52" s="127"/>
+      <c r="G52" s="127"/>
+      <c r="H52" s="127"/>
+    </row>
+    <row r="53" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="133" t="s">
+        <v>940</v>
+      </c>
+      <c r="B53" s="136" t="s">
+        <v>941</v>
+      </c>
+      <c r="C53" s="136" t="s">
+        <v>942</v>
+      </c>
+      <c r="D53" s="140" t="s">
+        <v>814</v>
+      </c>
+      <c r="E53" s="127"/>
+      <c r="F53" s="127"/>
+      <c r="G53" s="127"/>
+      <c r="H53" s="127"/>
+    </row>
+    <row r="54" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="133" t="s">
+        <v>943</v>
+      </c>
+      <c r="B54" s="136" t="s">
+        <v>944</v>
+      </c>
+      <c r="C54" s="136" t="s">
+        <v>945</v>
+      </c>
+      <c r="D54" s="140" t="s">
+        <v>912</v>
+      </c>
+      <c r="E54" s="127"/>
+      <c r="F54" s="127"/>
+      <c r="G54" s="127"/>
+      <c r="H54" s="127"/>
+    </row>
+    <row r="55" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="141" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="132" t="s">
+        <v>946</v>
+      </c>
+      <c r="C55" s="132" t="s">
+        <v>947</v>
+      </c>
+      <c r="D55" s="142" t="s">
+        <v>834</v>
+      </c>
+      <c r="E55" s="127"/>
+      <c r="F55" s="127"/>
+      <c r="G55" s="127"/>
+      <c r="H55" s="127"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5686B7FB-D686-FD47-ADB4-50E5785B6D50}">
   <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -9195,7 +12750,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="101" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -9205,7 +12760,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="103" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -9215,7 +12770,7 @@
       <c r="B4" s="54"/>
       <c r="C4" s="54"/>
       <c r="D4" s="12" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E4" s="54"/>
       <c r="F4" s="54"/>
@@ -9228,13 +12783,13 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E5" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F5" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -9242,30 +12797,30 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E6" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B7" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -9276,10 +12831,10 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E8" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -9290,24 +12845,24 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E9" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F9" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B10" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D10" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -9318,7 +12873,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
@@ -9331,153 +12886,153 @@
         <v>5</v>
       </c>
       <c r="B13" s="108" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C13" s="108" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D13" s="108" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E13" s="108" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F13" s="116"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B14" s="89" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C14" s="89" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D14" s="89" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E14" s="89" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B15" s="117" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D15" s="118" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E15" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B16" s="89" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C16" s="89" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D16" s="89" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E16" s="89" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B17" s="89" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C17" s="89" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D17" s="89" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E17" s="89" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B18" s="89" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C18" s="89" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D18" s="89" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E18" s="89" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B19" s="89" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C19" s="89" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D19" s="89" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E19" s="89" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E20" s="89" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B21" s="89" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C21" s="89" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D21" s="89" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E21" s="89" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -9485,21 +13040,21 @@
         <v>7</v>
       </c>
       <c r="B22" s="89" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C22" s="89" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D22" s="119" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E22" s="89" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B23" s="120">
         <v>0</v>
@@ -9511,34 +13066,34 @@
         <v>0</v>
       </c>
       <c r="E23" s="89" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B24" s="89" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C24" s="89" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D24" s="89" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E24" s="89" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
       <c r="D26" s="12" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E26" s="54"/>
       <c r="F26" s="54"/>
@@ -9548,16 +13103,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="E27" s="82" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F27" s="82" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -9568,13 +13123,13 @@
         <v>0.33</v>
       </c>
       <c r="D28" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E28" s="89">
         <v>73.790000000000006</v>
       </c>
       <c r="F28" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -9582,10 +13137,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E29" s="89">
         <v>89.95</v>
@@ -9596,13 +13151,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
         <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E30" s="89">
         <v>97.02</v>
@@ -9619,7 +13174,7 @@
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="E31" s="89">
         <v>127.6</v>
@@ -9630,13 +13185,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B32" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D32" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="E32" s="89">
         <v>151.22</v>
@@ -9647,36 +13202,36 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B33" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D33" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E33" s="117" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F33" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D34" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E34" s="117" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="F34" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -9684,30 +13239,30 @@
         <v>30</v>
       </c>
       <c r="B35" s="109" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B36" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B37" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="76" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -9720,11 +13275,11 @@
         <v>21</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C40" s="116"/>
       <c r="D40" s="18" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E40" s="116"/>
       <c r="F40" s="116"/>
@@ -9734,10 +13289,10 @@
         <v>46083</v>
       </c>
       <c r="B41" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D41" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -9745,10 +13300,10 @@
         <v>46080</v>
       </c>
       <c r="B42" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D42" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -9756,10 +13311,10 @@
         <v>46078</v>
       </c>
       <c r="B43" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D43" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -9767,10 +13322,10 @@
         <v>46028</v>
       </c>
       <c r="B44" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D44" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -9778,10 +13333,10 @@
         <v>46020</v>
       </c>
       <c r="B45" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D45" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -9789,10 +13344,10 @@
         <v>46013</v>
       </c>
       <c r="B46" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D46" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -9800,10 +13355,10 @@
         <v>45845</v>
       </c>
       <c r="B47" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D47" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -9811,15 +13366,15 @@
         <v>2024</v>
       </c>
       <c r="B48" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D48" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="76" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -9829,36 +13384,36 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="109" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B51" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B52" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="122" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B53" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="30" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="30" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -9867,9 +13422,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F24F8A94-CAFB-ED4A-8BD7-5C46C6CC39CB}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -9882,22 +13437,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -9908,16 +13463,16 @@
         <v>46085</v>
       </c>
       <c r="C2" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -9928,16 +13483,16 @@
         <v>46085</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F3" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -9948,16 +13503,16 @@
         <v>46085</v>
       </c>
       <c r="C4" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D4" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="E4" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="F4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -9968,16 +13523,16 @@
         <v>46085</v>
       </c>
       <c r="C5" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D5" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E5" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="F5" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -9988,16 +13543,16 @@
         <v>46085</v>
       </c>
       <c r="C6" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="D6" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="E6" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="F6" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -10008,16 +13563,16 @@
         <v>46085</v>
       </c>
       <c r="C7" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D7" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="E7" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="F7" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -10028,16 +13583,36 @@
         <v>46085</v>
       </c>
       <c r="C8" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="D8" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="E8" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="F8" t="s">
-        <v>737</v>
+        <v>742</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="46">
+        <v>46085</v>
+      </c>
+      <c r="C9" t="s">
+        <v>948</v>
+      </c>
+      <c r="D9" t="s">
+        <v>949</v>
+      </c>
+      <c r="E9" t="s">
+        <v>950</v>
+      </c>
+      <c r="F9" t="s">
+        <v>951</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samjo/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7705B6-6A46-CF48-A2FA-8C775014E3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A079D6-AC1C-2841-BB05-0DD21CFE789A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37960" yWindow="7460" windowWidth="30720" windowHeight="21680" firstSheet="2" activeTab="7" xr2:uid="{6AA5D1E0-5045-0A44-A426-F5E527A1D1E1}"/>
+    <workbookView xWindow="24980" yWindow="5560" windowWidth="43700" windowHeight="23240" firstSheet="2" activeTab="5" xr2:uid="{6AA5D1E0-5045-0A44-A426-F5E527A1D1E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Financial Statements" sheetId="6" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Company Overview" sheetId="10" r:id="rId7"/>
     <sheet name="Claude Log" sheetId="5" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1241,7 +1241,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Source: Q3 MDA FY2026, p.16</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Q3 MDA FY2026, p.16</t>
         </r>
       </text>
     </comment>
@@ -1289,7 +1298,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Source: battery-tech.net company profile</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: battery-tech.net company profile</t>
         </r>
       </text>
     </comment>
@@ -1361,7 +1379,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Source: firstphosphate.com, Feb 27 2025 NR</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: firstphosphate.com, Feb 27 2025 NR</t>
         </r>
       </text>
     </comment>
@@ -1385,7 +1412,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Source: battery-tech.net company profile</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: battery-tech.net company profile</t>
         </r>
       </text>
     </comment>
@@ -1553,7 +1589,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Source: Q3 MDA FY2026, p.17</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Q3 MDA FY2026, p.17</t>
         </r>
       </text>
     </comment>
@@ -1625,7 +1670,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Source: Q3 MDA FY2026, p.17</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Q3 MDA FY2026, p.17</t>
         </r>
       </text>
     </comment>
@@ -1769,7 +1823,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Source: Q3 MDA FY2026, p.17</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Q3 MDA FY2026, p.17</t>
         </r>
       </text>
     </comment>
@@ -2834,7 +2897,16 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Source: Q3 MDA FY2026, p.13</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Source: Q3 MDA FY2026, p.13</t>
         </r>
       </text>
     </comment>
@@ -3069,7 +3141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="956">
   <si>
     <t>COMPANY SNAPSHOT</t>
   </si>
@@ -5957,13 +6029,25 @@
   </si>
   <si>
     <t>Management &amp; Governance sheet now fully complete (A1:H55). All 5 sections populated with data. Text wrapping enabled. Column widths optimized for content.</t>
+  </si>
+  <si>
+    <t>User requested visual improvements to the Management &amp; Governance sheet.</t>
+  </si>
+  <si>
+    <t>Comprehensive visual overhaul of Management &amp; Governance sheet across 26 phases of formatting.</t>
+  </si>
+  <si>
+    <t>Applied: (1) Dark navy title banner with gradient subtitle colors, (2) Deep navy section headers with blue accent bottom borders, (3) Professional blue-white table column headers, (4) Alternating row colors (light blue/white) across all 5 sections, (5) Color-coded star ratings (green=5★, blue=4★, amber=3★), (6) Gold stars on dark navy for Overall Assessment row, (7) Full table borders with navy frames and light gray internal dividers, (8) Gold left-border accent on Assessment column, (9) Light yellow background for Assessment cells, (10) Green/red text for positive/negative investor implications, (11) Green/red text for Strengths vs Weaknesses in Section 5, (12) Highlighted CEO ownership (green bg), bold green insider buying for major buyers, (13) Optimized column widths (A:180, B:210, C:280, D:190, E:165, F:215, G:95, H:325), (14) Optimized row heights per section, (15) Frozen title rows (top 4), (16) Clean spacer rows between sections, (17) Centered dates/experience/ratings.</t>
+  </si>
+  <si>
+    <t>Management &amp; Governance sheet now has professional, visually cohesive formatting with clear hierarchy, color-coded data, and improved readability. All data preserved intact.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);&quot;-&quot;"/>
@@ -5976,8 +6060,9 @@
     <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.0,,&quot;M&quot;"/>
     <numFmt numFmtId="173" formatCode="\+0%;\-0%"/>
     <numFmt numFmtId="174" formatCode="&quot;$&quot;#,##0,,&quot;M&quot;"/>
+    <numFmt numFmtId="175" formatCode="yyyy"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="65" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -6304,38 +6389,157 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="10"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FFA8C4E0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF7A9BB5"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF1B3A5C"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFD700"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1A7A1A"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFD48B00"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A7A1A"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A7A1A"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCC3300"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1A5C1A"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8B2500"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1A7A1A"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1A7A1A"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6428,15 +6632,331 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6DCE4"/>
+        <fgColor rgb="FF0D2137"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B3A5C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E5984"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="25">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF4DA6FF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF4DA6FF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1B3A5C"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1B3A5C"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1B3A5C"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1B3A5C"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF1B3A5C"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1B3A5C"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1B3A5C"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D8E0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D8E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D8E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1B3A5C"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1B3A5C"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4DA6FF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D8E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D8E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4DA6FF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D8E0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4DA6FF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD4A017"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1B3A5C"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1B3A5C"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD4A017"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1B3A5C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD4A017"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1B3A5C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D8E0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D8E0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4A7FB5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF4A7FB5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1B3A5C"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4A7FB5"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1B3A5C"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4A7FB5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF4A7FB5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4A7FB5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1B3A5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D8E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D8E0"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -6445,7 +6965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6678,56 +7198,221 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="58" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="47" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="47" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="47" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6744,10 +7429,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8915,31 +9596,31 @@
         <v>194</v>
       </c>
       <c r="C10" s="44">
-        <f>(C9-B9)/B9</f>
+        <f t="shared" ref="C10:I10" si="0">(C9-B9)/B9</f>
         <v>1.4647584800159031E-2</v>
       </c>
       <c r="D10" s="44">
-        <f>(D9-C9)/C9</f>
+        <f t="shared" si="0"/>
         <v>1.6506452660344124E-2</v>
       </c>
       <c r="E10" s="44">
-        <f>(E9-D9)/D9</f>
+        <f t="shared" si="0"/>
         <v>1.4394027870093739E-2</v>
       </c>
       <c r="F10" s="44">
-        <f>(F9-E9)/E9</f>
+        <f t="shared" si="0"/>
         <v>0.16514179844397067</v>
       </c>
       <c r="G10" s="44">
-        <f>(G9-F9)/F9</f>
+        <f t="shared" si="0"/>
         <v>7.8671936270949719E-2</v>
       </c>
       <c r="H10" s="44">
-        <f>(H9-G9)/G9</f>
+        <f t="shared" si="0"/>
         <v>0.27336164876243535</v>
       </c>
       <c r="I10" s="44">
-        <f>(I9-H9)/H9</f>
+        <f t="shared" si="0"/>
         <v>0.2239830858195333</v>
       </c>
     </row>
@@ -8948,31 +9629,31 @@
         <v>195</v>
       </c>
       <c r="C11" s="44">
-        <f>C9/$B9-1</f>
+        <f t="shared" ref="C11:I11" si="1">C9/$B9-1</f>
         <v>1.4647584800159041E-2</v>
       </c>
       <c r="D11" s="44">
-        <f>D9/$B9-1</f>
+        <f t="shared" si="1"/>
         <v>3.1395817125595249E-2</v>
       </c>
       <c r="E11" s="44">
-        <f>E9/$B9-1</f>
+        <f t="shared" si="1"/>
         <v>4.6241757262399208E-2</v>
       </c>
       <c r="F11" s="44">
-        <f>F9/$B9-1</f>
+        <f t="shared" si="1"/>
         <v>0.21902000266389221</v>
       </c>
       <c r="G11" s="44">
-        <f>G9/$B9-1</f>
+        <f t="shared" si="1"/>
         <v>0.31492266662647883</v>
       </c>
       <c r="H11" s="44">
-        <f>H9/$B9-1</f>
+        <f t="shared" si="1"/>
         <v>0.67437209477059112</v>
       </c>
       <c r="I11" s="44">
-        <f>I9/$B9-1</f>
+        <f t="shared" si="1"/>
         <v>1.0494031233674241</v>
       </c>
     </row>
@@ -10711,35 +11392,35 @@
         <v>52</v>
       </c>
       <c r="B16" s="85">
-        <f>$B$5*B15</f>
+        <f t="shared" ref="B16:I16" si="0">$B$5*B15</f>
         <v>47700000</v>
       </c>
       <c r="C16" s="85">
-        <f>$B$5*C15</f>
+        <f t="shared" si="0"/>
         <v>79500000</v>
       </c>
       <c r="D16" s="85">
-        <f>$B$5*D15</f>
+        <f t="shared" si="0"/>
         <v>111300000.00000001</v>
       </c>
       <c r="E16" s="85">
-        <f>$B$5*E15</f>
+        <f t="shared" si="0"/>
         <v>159000000</v>
       </c>
       <c r="F16" s="86">
-        <f>$B$5*F15</f>
+        <f t="shared" si="0"/>
         <v>174900000</v>
       </c>
       <c r="G16" s="85">
-        <f>$B$5*G15</f>
+        <f t="shared" si="0"/>
         <v>238500000</v>
       </c>
       <c r="H16" s="85">
-        <f>$B$5*H15</f>
+        <f t="shared" si="0"/>
         <v>318000000</v>
       </c>
       <c r="I16" s="85">
-        <f>$B$5*I15</f>
+        <f t="shared" si="0"/>
         <v>397500000</v>
       </c>
     </row>
@@ -10748,35 +11429,35 @@
         <v>277</v>
       </c>
       <c r="B17" s="87">
-        <f>$B$5*B15/$B$7</f>
+        <f t="shared" ref="B17:I17" si="1">$B$5*B15/$B$7</f>
         <v>0.27529731720686668</v>
       </c>
       <c r="C17" s="87">
-        <f>$B$5*C15/$B$7</f>
+        <f t="shared" si="1"/>
         <v>0.45882886201144446</v>
       </c>
       <c r="D17" s="87">
-        <f>$B$5*D15/$B$7</f>
+        <f t="shared" si="1"/>
         <v>0.64236040681602224</v>
       </c>
       <c r="E17" s="87">
-        <f>$B$5*E15/$B$7</f>
+        <f t="shared" si="1"/>
         <v>0.91765772402288892</v>
       </c>
       <c r="F17" s="88">
-        <f>$B$5*F15/$B$7</f>
+        <f t="shared" si="1"/>
         <v>1.0094234964251778</v>
       </c>
       <c r="G17" s="87">
-        <f>$B$5*G15/$B$7</f>
+        <f t="shared" si="1"/>
         <v>1.3764865860343334</v>
       </c>
       <c r="H17" s="87">
-        <f>$B$5*H15/$B$7</f>
+        <f t="shared" si="1"/>
         <v>1.8353154480457778</v>
       </c>
       <c r="I17" s="87">
-        <f>$B$5*I15/$B$7</f>
+        <f t="shared" si="1"/>
         <v>2.2941443100572223</v>
       </c>
     </row>
@@ -10785,35 +11466,35 @@
         <v>278</v>
       </c>
       <c r="B18" s="87">
-        <f>$B$5*B15/$B$8</f>
+        <f t="shared" ref="B18:I18" si="2">$B$5*B15/$B$8</f>
         <v>0.24792099792099792</v>
       </c>
       <c r="C18" s="87">
-        <f>$B$5*C15/$B$8</f>
+        <f t="shared" si="2"/>
         <v>0.41320166320166318</v>
       </c>
       <c r="D18" s="87">
-        <f>$B$5*D15/$B$8</f>
+        <f t="shared" si="2"/>
         <v>0.57848232848232861</v>
       </c>
       <c r="E18" s="87">
-        <f>$B$5*E15/$B$8</f>
+        <f t="shared" si="2"/>
         <v>0.82640332640332637</v>
       </c>
       <c r="F18" s="88">
-        <f>$B$5*F15/$B$8</f>
+        <f t="shared" si="2"/>
         <v>0.90904365904365902</v>
       </c>
       <c r="G18" s="87">
-        <f>$B$5*G15/$B$8</f>
+        <f t="shared" si="2"/>
         <v>1.2396049896049897</v>
       </c>
       <c r="H18" s="87">
-        <f>$B$5*H15/$B$8</f>
+        <f t="shared" si="2"/>
         <v>1.6528066528066527</v>
       </c>
       <c r="I18" s="87">
-        <f>$B$5*I15/$B$8</f>
+        <f t="shared" si="2"/>
         <v>2.066008316008316</v>
       </c>
     </row>
@@ -10822,35 +11503,35 @@
         <v>53</v>
       </c>
       <c r="B19" s="90">
-        <f>B17/$B$6-1</f>
+        <f t="shared" ref="B19:I19" si="3">B17/$B$6-1</f>
         <v>-0.73781207885060318</v>
       </c>
       <c r="C19" s="90">
-        <f>C17/$B$6-1</f>
+        <f t="shared" si="3"/>
         <v>-0.56302013141767193</v>
       </c>
       <c r="D19" s="90">
-        <f>D17/$B$6-1</f>
+        <f t="shared" si="3"/>
         <v>-0.38822818398474079</v>
       </c>
       <c r="E19" s="90">
-        <f>E17/$B$6-1</f>
+        <f t="shared" si="3"/>
         <v>-0.12604026283534397</v>
       </c>
       <c r="F19" s="91">
-        <f>F17/$B$6-1</f>
+        <f t="shared" si="3"/>
         <v>-3.8644289118878294E-2</v>
       </c>
       <c r="G19" s="90">
-        <f>G17/$B$6-1</f>
+        <f t="shared" si="3"/>
         <v>0.3109396057469842</v>
       </c>
       <c r="H19" s="90">
-        <f>H17/$B$6-1</f>
+        <f t="shared" si="3"/>
         <v>0.74791947432931205</v>
       </c>
       <c r="I19" s="90">
-        <f>I17/$B$6-1</f>
+        <f t="shared" si="3"/>
         <v>1.1848993429116401</v>
       </c>
     </row>
@@ -11666,29 +12347,29 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="46.6640625" customWidth="1"/>
-    <col min="4" max="4" width="41.6640625" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" customWidth="1"/>
-    <col min="6" max="6" width="38.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="53.33203125" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="54.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="126" t="s">
         <v>743</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="128" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+    </row>
+    <row r="2" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="127" t="s">
         <v>744</v>
       </c>
       <c r="B2" s="127"/>
@@ -11699,1039 +12380,1049 @@
       <c r="G2" s="127"/>
       <c r="H2" s="127"/>
     </row>
-    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="129" t="s">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="128" t="s">
         <v>745</v>
       </c>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="127"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-    </row>
-    <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+    </row>
+    <row r="4" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="129"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+    </row>
+    <row r="5" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="130" t="s">
         <v>746</v>
       </c>
-      <c r="B5" s="131"/>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="131"/>
-    </row>
-    <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="132" t="s">
+      <c r="B5" s="130"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+    </row>
+    <row r="6" spans="1:8" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="188" t="s">
         <v>747</v>
       </c>
-      <c r="B6" s="132" t="s">
+      <c r="B6" s="180" t="s">
         <v>748</v>
       </c>
-      <c r="C6" s="132" t="s">
+      <c r="C6" s="180" t="s">
         <v>749</v>
       </c>
-      <c r="D6" s="132" t="s">
+      <c r="D6" s="180" t="s">
         <v>750</v>
       </c>
-      <c r="E6" s="132" t="s">
+      <c r="E6" s="180" t="s">
         <v>751</v>
       </c>
-      <c r="F6" s="132" t="s">
+      <c r="F6" s="180" t="s">
         <v>752</v>
       </c>
-      <c r="G6" s="132" t="s">
+      <c r="G6" s="179" t="s">
         <v>753</v>
       </c>
-      <c r="H6" s="132" t="s">
+      <c r="H6" s="153" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="133" t="s">
+    <row r="7" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="141" t="s">
         <v>754</v>
       </c>
-      <c r="B7" s="127" t="s">
+      <c r="B7" s="178" t="s">
         <v>755</v>
       </c>
-      <c r="C7" s="127" t="s">
+      <c r="C7" s="178" t="s">
         <v>756</v>
       </c>
-      <c r="D7" s="127" t="s">
+      <c r="D7" s="178" t="s">
         <v>757</v>
       </c>
-      <c r="E7" s="127" t="s">
+      <c r="E7" s="181" t="s">
         <v>758</v>
       </c>
-      <c r="F7" s="127" t="s">
+      <c r="F7" s="194" t="s">
         <v>759</v>
       </c>
-      <c r="G7" s="127" t="s">
+      <c r="G7" s="197" t="s">
         <v>760</v>
       </c>
-      <c r="H7" s="127" t="s">
+      <c r="H7" s="154" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="133" t="s">
+    <row r="8" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="139" t="s">
         <v>762</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="142" t="s">
         <v>763</v>
       </c>
-      <c r="C8" s="127" t="s">
+      <c r="C8" s="142" t="s">
         <v>764</v>
       </c>
-      <c r="D8" s="127" t="s">
+      <c r="D8" s="142" t="s">
         <v>765</v>
       </c>
-      <c r="E8" s="127" t="s">
+      <c r="E8" s="165" t="s">
         <v>766</v>
       </c>
-      <c r="F8" s="127" t="s">
+      <c r="F8" s="196" t="s">
         <v>767</v>
       </c>
-      <c r="G8" s="127" t="s">
+      <c r="G8" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="127" t="s">
+      <c r="H8" s="155" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="133" t="s">
+    <row r="9" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="140" t="s">
         <v>769</v>
       </c>
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="143" t="s">
         <v>770</v>
       </c>
-      <c r="C9" s="127" t="s">
+      <c r="C9" s="143" t="s">
         <v>771</v>
       </c>
-      <c r="D9" s="127" t="s">
+      <c r="D9" s="143" t="s">
         <v>772</v>
       </c>
-      <c r="E9" s="127" t="s">
+      <c r="E9" s="166" t="s">
         <v>773</v>
       </c>
-      <c r="F9" s="127" t="s">
+      <c r="F9" s="166" t="s">
         <v>774</v>
       </c>
-      <c r="G9" s="127" t="s">
+      <c r="G9" s="164" t="s">
         <v>775</v>
       </c>
-      <c r="H9" s="127" t="s">
+      <c r="H9" s="155" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="133" t="s">
+    <row r="10" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="139" t="s">
         <v>777</v>
       </c>
-      <c r="B10" s="127" t="s">
+      <c r="B10" s="142" t="s">
         <v>778</v>
       </c>
-      <c r="C10" s="127" t="s">
+      <c r="C10" s="142" t="s">
         <v>779</v>
       </c>
-      <c r="D10" s="127" t="s">
+      <c r="D10" s="142" t="s">
         <v>780</v>
       </c>
-      <c r="E10" s="127" t="s">
+      <c r="E10" s="165" t="s">
         <v>781</v>
       </c>
-      <c r="F10" s="127" t="s">
+      <c r="F10" s="165" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="127" t="s">
+      <c r="G10" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="127" t="s">
+      <c r="H10" s="155" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="133" t="s">
+    <row r="11" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="140" t="s">
         <v>783</v>
       </c>
-      <c r="B11" s="127" t="s">
+      <c r="B11" s="143" t="s">
         <v>784</v>
       </c>
-      <c r="C11" s="127" t="s">
+      <c r="C11" s="143" t="s">
         <v>785</v>
       </c>
-      <c r="D11" s="127" t="s">
+      <c r="D11" s="143" t="s">
         <v>786</v>
       </c>
-      <c r="E11" s="127" t="s">
+      <c r="E11" s="166" t="s">
         <v>787</v>
       </c>
-      <c r="F11" s="127" t="s">
+      <c r="F11" s="166" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="127" t="s">
+      <c r="G11" s="164" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="127" t="s">
+      <c r="H11" s="155" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="133" t="s">
+    <row r="12" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="139" t="s">
         <v>789</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="142" t="s">
         <v>790</v>
       </c>
-      <c r="C12" s="127" t="s">
+      <c r="C12" s="142" t="s">
         <v>791</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="142" t="s">
         <v>792</v>
       </c>
-      <c r="E12" s="127" t="s">
+      <c r="E12" s="165" t="s">
         <v>793</v>
       </c>
-      <c r="F12" s="127" t="s">
+      <c r="F12" s="165" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="127" t="s">
+      <c r="G12" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="127" t="s">
+      <c r="H12" s="155" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="133" t="s">
+    <row r="13" spans="1:8" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="140" t="s">
         <v>795</v>
       </c>
-      <c r="B13" s="127" t="s">
+      <c r="B13" s="143" t="s">
         <v>796</v>
       </c>
-      <c r="C13" s="127" t="s">
+      <c r="C13" s="143" t="s">
         <v>797</v>
       </c>
-      <c r="D13" s="127" t="s">
+      <c r="D13" s="143" t="s">
         <v>798</v>
       </c>
-      <c r="E13" s="127" t="s">
+      <c r="E13" s="166" t="s">
         <v>799</v>
       </c>
-      <c r="F13" s="127" t="s">
+      <c r="F13" s="195" t="s">
         <v>800</v>
       </c>
-      <c r="G13" s="127" t="s">
+      <c r="G13" s="164" t="s">
         <v>801</v>
       </c>
-      <c r="H13" s="127" t="s">
+      <c r="H13" s="156" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="127"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-    </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="151"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="151"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="151"/>
+      <c r="H14" s="150"/>
+    </row>
+    <row r="15" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="130" t="s">
         <v>803</v>
       </c>
-      <c r="B15" s="131"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="131"/>
-    </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="132" t="s">
+      <c r="B15" s="130"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+    </row>
+    <row r="16" spans="1:8" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="188" t="s">
         <v>747</v>
       </c>
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="180" t="s">
         <v>804</v>
       </c>
-      <c r="C16" s="132" t="s">
+      <c r="C16" s="180" t="s">
         <v>749</v>
       </c>
-      <c r="D16" s="132" t="s">
+      <c r="D16" s="180" t="s">
         <v>805</v>
       </c>
-      <c r="E16" s="132" t="s">
+      <c r="E16" s="180" t="s">
         <v>806</v>
       </c>
-      <c r="F16" s="132" t="s">
+      <c r="F16" s="180" t="s">
         <v>807</v>
       </c>
-      <c r="G16" s="132" t="s">
+      <c r="G16" s="179" t="s">
         <v>808</v>
       </c>
-      <c r="H16" s="132" t="s">
+      <c r="H16" s="153" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="133" t="s">
+    <row r="17" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="141" t="s">
         <v>809</v>
       </c>
-      <c r="B17" s="127" t="s">
+      <c r="B17" s="178" t="s">
         <v>810</v>
       </c>
-      <c r="C17" s="127" t="s">
+      <c r="C17" s="178" t="s">
         <v>811</v>
       </c>
-      <c r="D17" s="127" t="s">
+      <c r="D17" s="178" t="s">
         <v>812</v>
       </c>
-      <c r="E17" s="134">
+      <c r="E17" s="190">
         <v>44835</v>
       </c>
-      <c r="F17" s="127" t="s">
+      <c r="F17" s="178" t="s">
         <v>813</v>
       </c>
-      <c r="G17" s="127" t="s">
+      <c r="G17" s="182" t="s">
         <v>814</v>
       </c>
-      <c r="H17" s="127" t="s">
+      <c r="H17" s="154" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="133" t="s">
+    <row r="18" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="139" t="s">
         <v>816</v>
       </c>
-      <c r="B18" s="127" t="s">
+      <c r="B18" s="142" t="s">
         <v>817</v>
       </c>
-      <c r="C18" s="127" t="s">
+      <c r="C18" s="142" t="s">
         <v>818</v>
       </c>
-      <c r="D18" s="127" t="s">
+      <c r="D18" s="142" t="s">
         <v>819</v>
       </c>
-      <c r="E18" s="127" t="s">
+      <c r="E18" s="191" t="s">
         <v>820</v>
       </c>
-      <c r="F18" s="127" t="s">
+      <c r="F18" s="142" t="s">
         <v>821</v>
       </c>
-      <c r="G18" s="127" t="s">
+      <c r="G18" s="157" t="s">
         <v>814</v>
       </c>
-      <c r="H18" s="127" t="s">
+      <c r="H18" s="155" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="133" t="s">
+    <row r="19" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="140" t="s">
         <v>823</v>
       </c>
-      <c r="B19" s="127" t="s">
+      <c r="B19" s="143" t="s">
         <v>824</v>
       </c>
-      <c r="C19" s="127" t="s">
+      <c r="C19" s="143" t="s">
         <v>825</v>
       </c>
-      <c r="D19" s="127" t="s">
+      <c r="D19" s="143" t="s">
         <v>826</v>
       </c>
-      <c r="E19" s="134">
+      <c r="E19" s="192">
         <v>45383</v>
       </c>
-      <c r="F19" s="127" t="s">
+      <c r="F19" s="143" t="s">
         <v>827</v>
       </c>
-      <c r="G19" s="127" t="s">
+      <c r="G19" s="158" t="s">
         <v>814</v>
       </c>
-      <c r="H19" s="127" t="s">
+      <c r="H19" s="155" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="133" t="s">
+    <row r="20" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="139" t="s">
         <v>829</v>
       </c>
-      <c r="B20" s="127" t="s">
+      <c r="B20" s="142" t="s">
         <v>830</v>
       </c>
-      <c r="C20" s="127" t="s">
+      <c r="C20" s="142" t="s">
         <v>831</v>
       </c>
-      <c r="D20" s="127" t="s">
+      <c r="D20" s="142" t="s">
         <v>832</v>
       </c>
-      <c r="E20" s="127" t="s">
+      <c r="E20" s="191" t="s">
         <v>820</v>
       </c>
-      <c r="F20" s="127" t="s">
+      <c r="F20" s="142" t="s">
         <v>833</v>
       </c>
-      <c r="G20" s="127" t="s">
+      <c r="G20" s="159" t="s">
         <v>834</v>
       </c>
-      <c r="H20" s="127" t="s">
+      <c r="H20" s="155" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="133" t="s">
+    <row r="21" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="140" t="s">
         <v>836</v>
       </c>
-      <c r="B21" s="127" t="s">
+      <c r="B21" s="143" t="s">
         <v>837</v>
       </c>
-      <c r="C21" s="127" t="s">
+      <c r="C21" s="143" t="s">
         <v>838</v>
       </c>
-      <c r="D21" s="127" t="s">
+      <c r="D21" s="143" t="s">
         <v>839</v>
       </c>
-      <c r="E21" s="127" t="s">
+      <c r="E21" s="192" t="s">
         <v>820</v>
       </c>
-      <c r="F21" s="127" t="s">
+      <c r="F21" s="143" t="s">
         <v>840</v>
       </c>
-      <c r="G21" s="127" t="s">
+      <c r="G21" s="160" t="s">
         <v>834</v>
       </c>
-      <c r="H21" s="127" t="s">
+      <c r="H21" s="155" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="133" t="s">
+    <row r="22" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="139" t="s">
         <v>842</v>
       </c>
-      <c r="B22" s="127" t="s">
+      <c r="B22" s="142" t="s">
         <v>843</v>
       </c>
-      <c r="C22" s="127" t="s">
+      <c r="C22" s="142" t="s">
         <v>844</v>
       </c>
-      <c r="D22" s="127" t="s">
+      <c r="D22" s="142" t="s">
         <v>845</v>
       </c>
-      <c r="E22" s="127" t="s">
+      <c r="E22" s="191" t="s">
         <v>820</v>
       </c>
-      <c r="F22" s="127" t="s">
+      <c r="F22" s="142" t="s">
         <v>846</v>
       </c>
-      <c r="G22" s="127" t="s">
+      <c r="G22" s="159" t="s">
         <v>834</v>
       </c>
-      <c r="H22" s="127" t="s">
+      <c r="H22" s="155" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="133" t="s">
+    <row r="23" spans="1:8" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="140" t="s">
         <v>848</v>
       </c>
-      <c r="B23" s="127" t="s">
+      <c r="B23" s="143" t="s">
         <v>849</v>
       </c>
-      <c r="C23" s="127" t="s">
+      <c r="C23" s="143" t="s">
         <v>850</v>
       </c>
-      <c r="D23" s="127" t="s">
+      <c r="D23" s="143" t="s">
         <v>851</v>
       </c>
-      <c r="E23" s="127" t="s">
+      <c r="E23" s="192" t="s">
         <v>852</v>
       </c>
-      <c r="F23" s="127" t="s">
+      <c r="F23" s="143" t="s">
         <v>853</v>
       </c>
-      <c r="G23" s="127" t="s">
+      <c r="G23" s="158" t="s">
         <v>814</v>
       </c>
-      <c r="H23" s="127" t="s">
+      <c r="H23" s="156" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="127"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-    </row>
-    <row r="25" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="151"/>
+      <c r="B24" s="151"/>
+      <c r="C24" s="151"/>
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="150"/>
+    </row>
+    <row r="25" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="130" t="s">
         <v>855</v>
       </c>
-      <c r="B25" s="131"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="131"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="131"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="131"/>
-    </row>
-    <row r="26" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="132" t="s">
+      <c r="B25" s="130"/>
+      <c r="C25" s="130"/>
+      <c r="D25" s="130"/>
+      <c r="E25" s="130"/>
+      <c r="F25" s="130"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="130"/>
+    </row>
+    <row r="26" spans="1:8" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="188" t="s">
         <v>747</v>
       </c>
-      <c r="B26" s="132" t="s">
+      <c r="B26" s="180" t="s">
         <v>856</v>
       </c>
-      <c r="C26" s="132" t="s">
+      <c r="C26" s="180" t="s">
         <v>749</v>
       </c>
-      <c r="D26" s="132" t="s">
+      <c r="D26" s="180" t="s">
         <v>805</v>
       </c>
-      <c r="E26" s="132" t="s">
+      <c r="E26" s="180" t="s">
         <v>857</v>
       </c>
-      <c r="F26" s="132" t="s">
+      <c r="F26" s="180" t="s">
         <v>858</v>
       </c>
-      <c r="G26" s="135"/>
-      <c r="H26" s="132" t="s">
+      <c r="G26" s="179"/>
+      <c r="H26" s="153" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="133" t="s">
+    <row r="27" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="141" t="s">
         <v>859</v>
       </c>
-      <c r="B27" s="127" t="s">
+      <c r="B27" s="178" t="s">
         <v>860</v>
       </c>
-      <c r="C27" s="127" t="s">
+      <c r="C27" s="178" t="s">
         <v>861</v>
       </c>
-      <c r="D27" s="127" t="s">
+      <c r="D27" s="178" t="s">
         <v>862</v>
       </c>
-      <c r="E27" s="127" t="s">
+      <c r="E27" s="193" t="s">
         <v>863</v>
       </c>
-      <c r="F27" s="127" t="s">
+      <c r="F27" s="178" t="s">
         <v>864</v>
       </c>
-      <c r="G27" s="127"/>
-      <c r="H27" s="127" t="s">
+      <c r="G27" s="178"/>
+      <c r="H27" s="154" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="133" t="s">
+    <row r="28" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="139" t="s">
         <v>866</v>
       </c>
-      <c r="B28" s="127" t="s">
+      <c r="B28" s="142" t="s">
         <v>867</v>
       </c>
-      <c r="C28" s="127" t="s">
+      <c r="C28" s="142" t="s">
         <v>868</v>
       </c>
-      <c r="D28" s="127" t="s">
+      <c r="D28" s="142" t="s">
         <v>869</v>
       </c>
-      <c r="E28" s="127" t="s">
+      <c r="E28" s="161" t="s">
         <v>863</v>
       </c>
-      <c r="F28" s="127" t="s">
+      <c r="F28" s="142" t="s">
         <v>870</v>
       </c>
-      <c r="G28" s="127"/>
-      <c r="H28" s="127" t="s">
+      <c r="G28" s="142"/>
+      <c r="H28" s="155" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="133" t="s">
+    <row r="29" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="140" t="s">
         <v>872</v>
       </c>
-      <c r="B29" s="127" t="s">
+      <c r="B29" s="143" t="s">
         <v>873</v>
       </c>
-      <c r="C29" s="127" t="s">
+      <c r="C29" s="143" t="s">
         <v>874</v>
       </c>
-      <c r="D29" s="127" t="s">
+      <c r="D29" s="143" t="s">
         <v>875</v>
       </c>
-      <c r="E29" s="127" t="s">
+      <c r="E29" s="163" t="s">
         <v>863</v>
       </c>
-      <c r="F29" s="127" t="s">
+      <c r="F29" s="143" t="s">
         <v>876</v>
       </c>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127" t="s">
+      <c r="G29" s="143"/>
+      <c r="H29" s="155" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="133" t="s">
+    <row r="30" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="139" t="s">
         <v>878</v>
       </c>
-      <c r="B30" s="127" t="s">
+      <c r="B30" s="142" t="s">
         <v>879</v>
       </c>
-      <c r="C30" s="127" t="s">
+      <c r="C30" s="142" t="s">
         <v>880</v>
       </c>
-      <c r="D30" s="127" t="s">
+      <c r="D30" s="142" t="s">
         <v>881</v>
       </c>
-      <c r="E30" s="127" t="s">
+      <c r="E30" s="161" t="s">
         <v>882</v>
       </c>
-      <c r="F30" s="127" t="s">
+      <c r="F30" s="142" t="s">
         <v>883</v>
       </c>
-      <c r="G30" s="127"/>
-      <c r="H30" s="127" t="s">
+      <c r="G30" s="142"/>
+      <c r="H30" s="155" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="133" t="s">
+    <row r="31" spans="1:8" ht="58" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="140" t="s">
         <v>885</v>
       </c>
-      <c r="B31" s="127" t="s">
+      <c r="B31" s="143" t="s">
         <v>886</v>
       </c>
-      <c r="C31" s="127" t="s">
+      <c r="C31" s="143" t="s">
         <v>887</v>
       </c>
-      <c r="D31" s="127" t="s">
+      <c r="D31" s="143" t="s">
         <v>888</v>
       </c>
-      <c r="E31" s="127" t="s">
+      <c r="E31" s="163" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="127" t="s">
+      <c r="F31" s="143" t="s">
         <v>889</v>
       </c>
-      <c r="G31" s="127"/>
-      <c r="H31" s="127" t="s">
+      <c r="G31" s="143"/>
+      <c r="H31" s="155" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="133" t="s">
+    <row r="32" spans="1:8" ht="58" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="139" t="s">
         <v>891</v>
       </c>
-      <c r="B32" s="127" t="s">
+      <c r="B32" s="142" t="s">
         <v>892</v>
       </c>
-      <c r="C32" s="127" t="s">
+      <c r="C32" s="142" t="s">
         <v>893</v>
       </c>
-      <c r="D32" s="127" t="s">
+      <c r="D32" s="142" t="s">
         <v>894</v>
       </c>
-      <c r="E32" s="127" t="s">
+      <c r="E32" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="127" t="s">
+      <c r="F32" s="142" t="s">
         <v>895</v>
       </c>
-      <c r="G32" s="127"/>
-      <c r="H32" s="127" t="s">
+      <c r="G32" s="142"/>
+      <c r="H32" s="156" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="127"/>
-      <c r="B33" s="127"/>
-      <c r="C33" s="127"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="127"/>
-    </row>
-    <row r="34" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="151"/>
+      <c r="B33" s="151"/>
+      <c r="C33" s="151"/>
+      <c r="D33" s="151"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="151"/>
+      <c r="G33" s="151"/>
+      <c r="H33" s="150"/>
+    </row>
+    <row r="34" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="130" t="s">
         <v>897</v>
       </c>
-      <c r="B34" s="131"/>
-      <c r="C34" s="131"/>
-      <c r="D34" s="131"/>
-      <c r="E34" s="131"/>
-      <c r="F34" s="131"/>
-      <c r="G34" s="131"/>
-      <c r="H34" s="131"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="127"/>
-      <c r="B35" s="127"/>
-      <c r="C35" s="127"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-    </row>
-    <row r="36" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="132" t="s">
+      <c r="B34" s="130"/>
+      <c r="C34" s="130"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="130"/>
+      <c r="H34" s="130"/>
+    </row>
+    <row r="35" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="152"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="152"/>
+    </row>
+    <row r="36" spans="1:8" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="189" t="s">
         <v>898</v>
       </c>
-      <c r="B36" s="132" t="s">
+      <c r="B36" s="185" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="132" t="s">
+      <c r="C36" s="183" t="s">
         <v>899</v>
       </c>
-      <c r="D36" s="132" t="s">
+      <c r="D36" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="127"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="127"/>
-      <c r="H36" s="127"/>
-    </row>
-    <row r="37" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="136" t="s">
+      <c r="E36" s="150"/>
+      <c r="F36" s="150"/>
+      <c r="G36" s="150"/>
+      <c r="H36" s="150"/>
+    </row>
+    <row r="37" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="146" t="s">
         <v>900</v>
       </c>
-      <c r="B37" s="127" t="s">
+      <c r="B37" s="178" t="s">
         <v>901</v>
       </c>
-      <c r="C37" s="137" t="s">
+      <c r="C37" s="186" t="s">
         <v>902</v>
       </c>
-      <c r="D37" s="127" t="s">
+      <c r="D37" s="132" t="s">
         <v>814</v>
       </c>
-      <c r="E37" s="127"/>
-      <c r="F37" s="127"/>
-      <c r="G37" s="127"/>
-      <c r="H37" s="127"/>
-    </row>
-    <row r="38" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="136" t="s">
+      <c r="E37" s="150"/>
+      <c r="F37" s="150"/>
+      <c r="G37" s="150"/>
+      <c r="H37" s="150"/>
+    </row>
+    <row r="38" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="144" t="s">
         <v>903</v>
       </c>
-      <c r="B38" s="127" t="s">
+      <c r="B38" s="142" t="s">
         <v>904</v>
       </c>
-      <c r="C38" s="137" t="s">
+      <c r="C38" s="167" t="s">
         <v>905</v>
       </c>
-      <c r="D38" s="127" t="s">
+      <c r="D38" s="133" t="s">
         <v>814</v>
       </c>
-      <c r="E38" s="127"/>
-      <c r="F38" s="127"/>
-      <c r="G38" s="127"/>
-      <c r="H38" s="127"/>
-    </row>
-    <row r="39" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="136" t="s">
+      <c r="E38" s="150"/>
+      <c r="F38" s="150"/>
+      <c r="G38" s="150"/>
+      <c r="H38" s="150"/>
+    </row>
+    <row r="39" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="145" t="s">
         <v>906</v>
       </c>
-      <c r="B39" s="127" t="s">
+      <c r="B39" s="143" t="s">
         <v>907</v>
       </c>
-      <c r="C39" s="137" t="s">
+      <c r="C39" s="168" t="s">
         <v>908</v>
       </c>
-      <c r="D39" s="127" t="s">
+      <c r="D39" s="134" t="s">
         <v>834</v>
       </c>
-      <c r="E39" s="127"/>
-      <c r="F39" s="127"/>
-      <c r="G39" s="127"/>
-      <c r="H39" s="127"/>
-    </row>
-    <row r="40" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="136" t="s">
+      <c r="E39" s="150"/>
+      <c r="F39" s="150"/>
+      <c r="G39" s="150"/>
+      <c r="H39" s="150"/>
+    </row>
+    <row r="40" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="144" t="s">
         <v>909</v>
       </c>
-      <c r="B40" s="127" t="s">
+      <c r="B40" s="142" t="s">
         <v>910</v>
       </c>
-      <c r="C40" s="138" t="s">
+      <c r="C40" s="170" t="s">
         <v>911</v>
       </c>
-      <c r="D40" s="127" t="s">
+      <c r="D40" s="135" t="s">
         <v>912</v>
       </c>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-      <c r="G40" s="127"/>
-      <c r="H40" s="127"/>
-    </row>
-    <row r="41" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="136" t="s">
+      <c r="E40" s="150"/>
+      <c r="F40" s="150"/>
+      <c r="G40" s="150"/>
+      <c r="H40" s="150"/>
+    </row>
+    <row r="41" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="145" t="s">
         <v>913</v>
       </c>
-      <c r="B41" s="127" t="s">
+      <c r="B41" s="143" t="s">
         <v>914</v>
       </c>
-      <c r="C41" s="137" t="s">
+      <c r="C41" s="168" t="s">
         <v>915</v>
       </c>
-      <c r="D41" s="127" t="s">
+      <c r="D41" s="134" t="s">
         <v>834</v>
       </c>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-    </row>
-    <row r="42" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="136" t="s">
+      <c r="E41" s="150"/>
+      <c r="F41" s="150"/>
+      <c r="G41" s="150"/>
+      <c r="H41" s="150"/>
+    </row>
+    <row r="42" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="144" t="s">
         <v>916</v>
       </c>
-      <c r="B42" s="127" t="s">
+      <c r="B42" s="142" t="s">
         <v>917</v>
       </c>
-      <c r="C42" s="139" t="s">
+      <c r="C42" s="169" t="s">
         <v>918</v>
       </c>
-      <c r="D42" s="127" t="s">
+      <c r="D42" s="133" t="s">
         <v>814</v>
       </c>
-      <c r="E42" s="127"/>
-      <c r="F42" s="127"/>
-      <c r="G42" s="127"/>
-      <c r="H42" s="127"/>
-    </row>
-    <row r="43" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="136" t="s">
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="150"/>
+    </row>
+    <row r="43" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="145" t="s">
         <v>919</v>
       </c>
-      <c r="B43" s="127" t="s">
+      <c r="B43" s="143" t="s">
         <v>920</v>
       </c>
-      <c r="C43" s="137" t="s">
+      <c r="C43" s="168" t="s">
         <v>921</v>
       </c>
-      <c r="D43" s="127" t="s">
+      <c r="D43" s="137" t="s">
         <v>814</v>
       </c>
-      <c r="E43" s="127"/>
-      <c r="F43" s="127"/>
-      <c r="G43" s="127"/>
-      <c r="H43" s="127"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="127"/>
-      <c r="B44" s="127"/>
-      <c r="C44" s="127"/>
-      <c r="D44" s="127"/>
-      <c r="E44" s="127"/>
-      <c r="F44" s="127"/>
-      <c r="G44" s="127"/>
-      <c r="H44" s="127"/>
-    </row>
-    <row r="45" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E43" s="150"/>
+      <c r="F43" s="150"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="150"/>
+    </row>
+    <row r="44" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="150"/>
+      <c r="B44" s="150"/>
+      <c r="C44" s="150"/>
+      <c r="D44" s="150"/>
+      <c r="E44" s="150"/>
+      <c r="F44" s="150"/>
+      <c r="G44" s="150"/>
+      <c r="H44" s="150"/>
+    </row>
+    <row r="45" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="130" t="s">
         <v>922</v>
       </c>
-      <c r="B45" s="131"/>
-      <c r="C45" s="131"/>
-      <c r="D45" s="131"/>
-      <c r="E45" s="131"/>
-      <c r="F45" s="131"/>
-      <c r="G45" s="131"/>
-      <c r="H45" s="131"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="127"/>
-      <c r="B46" s="127"/>
-      <c r="C46" s="127"/>
-      <c r="D46" s="127"/>
-      <c r="E46" s="127"/>
-      <c r="F46" s="127"/>
-      <c r="G46" s="127"/>
-      <c r="H46" s="127"/>
-    </row>
-    <row r="47" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="132" t="s">
+      <c r="B45" s="130"/>
+      <c r="C45" s="130"/>
+      <c r="D45" s="130"/>
+      <c r="E45" s="130"/>
+      <c r="F45" s="130"/>
+      <c r="G45" s="130"/>
+      <c r="H45" s="130"/>
+    </row>
+    <row r="46" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="152"/>
+      <c r="B46" s="152"/>
+      <c r="C46" s="152"/>
+      <c r="D46" s="152"/>
+      <c r="E46" s="152"/>
+      <c r="F46" s="152"/>
+      <c r="G46" s="152"/>
+      <c r="H46" s="152"/>
+    </row>
+    <row r="47" spans="1:8" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="189" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="132" t="s">
+      <c r="B47" s="185" t="s">
         <v>923</v>
       </c>
-      <c r="C47" s="132" t="s">
+      <c r="C47" s="183" t="s">
         <v>924</v>
       </c>
-      <c r="D47" s="132" t="s">
+      <c r="D47" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="E47" s="127"/>
-      <c r="F47" s="127"/>
-      <c r="G47" s="127"/>
-      <c r="H47" s="127"/>
+      <c r="E47" s="150"/>
+      <c r="F47" s="150"/>
+      <c r="G47" s="150"/>
+      <c r="H47" s="150"/>
     </row>
     <row r="48" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="133" t="s">
+      <c r="A48" s="146" t="s">
         <v>925</v>
       </c>
-      <c r="B48" s="136" t="s">
+      <c r="B48" s="184" t="s">
         <v>926</v>
       </c>
-      <c r="C48" s="136" t="s">
+      <c r="C48" s="187" t="s">
         <v>927</v>
       </c>
-      <c r="D48" s="140" t="s">
+      <c r="D48" s="136" t="s">
         <v>834</v>
       </c>
-      <c r="E48" s="127"/>
-      <c r="F48" s="127"/>
-      <c r="G48" s="127"/>
-      <c r="H48" s="127"/>
+      <c r="E48" s="150"/>
+      <c r="F48" s="150"/>
+      <c r="G48" s="150"/>
+      <c r="H48" s="150"/>
     </row>
     <row r="49" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="133" t="s">
+      <c r="A49" s="144" t="s">
         <v>928</v>
       </c>
-      <c r="B49" s="136" t="s">
+      <c r="B49" s="171" t="s">
         <v>929</v>
       </c>
-      <c r="C49" s="136" t="s">
+      <c r="C49" s="175" t="s">
         <v>930</v>
       </c>
-      <c r="D49" s="140" t="s">
+      <c r="D49" s="135" t="s">
         <v>912</v>
       </c>
-      <c r="E49" s="127"/>
-      <c r="F49" s="127"/>
-      <c r="G49" s="127"/>
-      <c r="H49" s="127"/>
+      <c r="E49" s="150"/>
+      <c r="F49" s="150"/>
+      <c r="G49" s="150"/>
+      <c r="H49" s="150"/>
     </row>
     <row r="50" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="133" t="s">
+      <c r="A50" s="145" t="s">
         <v>931</v>
       </c>
-      <c r="B50" s="136" t="s">
+      <c r="B50" s="172" t="s">
         <v>932</v>
       </c>
-      <c r="C50" s="136" t="s">
+      <c r="C50" s="176" t="s">
         <v>933</v>
       </c>
-      <c r="D50" s="140" t="s">
+      <c r="D50" s="137" t="s">
         <v>814</v>
       </c>
-      <c r="E50" s="127"/>
-      <c r="F50" s="127"/>
-      <c r="G50" s="127"/>
-      <c r="H50" s="127"/>
+      <c r="E50" s="150"/>
+      <c r="F50" s="150"/>
+      <c r="G50" s="150"/>
+      <c r="H50" s="150"/>
     </row>
     <row r="51" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="133" t="s">
+      <c r="A51" s="144" t="s">
         <v>934</v>
       </c>
-      <c r="B51" s="136" t="s">
+      <c r="B51" s="171" t="s">
         <v>935</v>
       </c>
-      <c r="C51" s="136" t="s">
+      <c r="C51" s="175" t="s">
         <v>936</v>
       </c>
-      <c r="D51" s="140" t="s">
+      <c r="D51" s="133" t="s">
         <v>814</v>
       </c>
-      <c r="E51" s="127"/>
-      <c r="F51" s="127"/>
-      <c r="G51" s="127"/>
-      <c r="H51" s="127"/>
+      <c r="E51" s="150"/>
+      <c r="F51" s="150"/>
+      <c r="G51" s="150"/>
+      <c r="H51" s="150"/>
     </row>
     <row r="52" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="133" t="s">
+      <c r="A52" s="145" t="s">
         <v>937</v>
       </c>
-      <c r="B52" s="136" t="s">
+      <c r="B52" s="172" t="s">
         <v>938</v>
       </c>
-      <c r="C52" s="136" t="s">
+      <c r="C52" s="176" t="s">
         <v>939</v>
       </c>
-      <c r="D52" s="140" t="s">
+      <c r="D52" s="137" t="s">
         <v>814</v>
       </c>
-      <c r="E52" s="127"/>
-      <c r="F52" s="127"/>
-      <c r="G52" s="127"/>
-      <c r="H52" s="127"/>
+      <c r="E52" s="150"/>
+      <c r="F52" s="150"/>
+      <c r="G52" s="150"/>
+      <c r="H52" s="150"/>
     </row>
     <row r="53" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="133" t="s">
+      <c r="A53" s="144" t="s">
         <v>940</v>
       </c>
-      <c r="B53" s="136" t="s">
+      <c r="B53" s="171" t="s">
         <v>941</v>
       </c>
-      <c r="C53" s="136" t="s">
+      <c r="C53" s="175" t="s">
         <v>942</v>
       </c>
-      <c r="D53" s="140" t="s">
+      <c r="D53" s="133" t="s">
         <v>814</v>
       </c>
-      <c r="E53" s="127"/>
-      <c r="F53" s="127"/>
-      <c r="G53" s="127"/>
-      <c r="H53" s="127"/>
-    </row>
-    <row r="54" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="133" t="s">
+      <c r="E53" s="150"/>
+      <c r="F53" s="150"/>
+      <c r="G53" s="150"/>
+      <c r="H53" s="150"/>
+    </row>
+    <row r="54" spans="1:8" ht="65" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="149" t="s">
         <v>943</v>
       </c>
-      <c r="B54" s="136" t="s">
+      <c r="B54" s="173" t="s">
         <v>944</v>
       </c>
-      <c r="C54" s="136" t="s">
+      <c r="C54" s="177" t="s">
         <v>945</v>
       </c>
-      <c r="D54" s="140" t="s">
+      <c r="D54" s="138" t="s">
         <v>912</v>
       </c>
-      <c r="E54" s="127"/>
-      <c r="F54" s="127"/>
-      <c r="G54" s="127"/>
-      <c r="H54" s="127"/>
-    </row>
-    <row r="55" spans="1:8" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="141" t="s">
+      <c r="E54" s="150"/>
+      <c r="F54" s="150"/>
+      <c r="G54" s="150"/>
+      <c r="H54" s="150"/>
+    </row>
+    <row r="55" spans="1:8" ht="85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="148" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="132" t="s">
+      <c r="B55" s="174" t="s">
         <v>946</v>
       </c>
-      <c r="C55" s="132" t="s">
+      <c r="C55" s="174" t="s">
         <v>947</v>
       </c>
-      <c r="D55" s="142" t="s">
+      <c r="D55" s="147" t="s">
         <v>834</v>
       </c>
-      <c r="E55" s="127"/>
-      <c r="F55" s="127"/>
-      <c r="G55" s="127"/>
-      <c r="H55" s="127"/>
+      <c r="E55" s="150"/>
+      <c r="F55" s="150"/>
+      <c r="G55" s="150"/>
+      <c r="H55" s="150"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A25:H25"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -13424,7 +14115,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F24F8A94-CAFB-ED4A-8BD7-5C46C6CC39CB}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -13615,6 +14306,26 @@
         <v>951</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="46">
+        <v>46085</v>
+      </c>
+      <c r="C10" t="s">
+        <v>952</v>
+      </c>
+      <c r="D10" t="s">
+        <v>953</v>
+      </c>
+      <c r="E10" t="s">
+        <v>954</v>
+      </c>
+      <c r="F10" t="s">
+        <v>955</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
